--- a/PUM.DE.xlsx
+++ b/PUM.DE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06B64CA-044B-4B59-9134-47C7149FDA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA2B566-5B9B-4899-97E8-6C276AE17A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{DF056538-1695-47DF-BC32-BA7DD1F9A83B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{DF056538-1695-47DF-BC32-BA7DD1F9A83B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
   <si>
     <t xml:space="preserve">Puma </t>
   </si>
@@ -203,21 +203,34 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>CEO:</t>
+  </si>
+  <si>
+    <t>Arthur Hoeld</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -280,25 +293,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -635,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46746356-DDAA-46AE-8571-B699D0C98654}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="2" customWidth="1"/>
@@ -655,7 +674,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>23.45</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -663,10 +682,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="4">
-        <v>147.13666000000001</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>50</v>
+        <v>147.41</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -678,7 +697,7 @@
       </c>
       <c r="I4" s="4">
         <f>+I2*I3</f>
-        <v>3450.3546770000003</v>
+        <v>3545.2105000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -689,10 +708,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="4">
-        <v>292.60000000000002</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>290</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -700,11 +719,11 @@
         <v>6</v>
       </c>
       <c r="I6" s="4">
-        <f>984.1+359.8</f>
-        <v>1343.9</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>50</v>
+        <f>424.2+144.1+3.7</f>
+        <v>572</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -713,11 +732,19 @@
       </c>
       <c r="I7" s="4">
         <f>+I4-I5+I6</f>
-        <v>4501.6546770000004</v>
+        <v>3827.2105000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="I8" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H10" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -805,47 +832,53 @@
       <c r="B3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13">
         <v>667.9</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="13">
         <v>855.7</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="13">
         <v>817.9</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="13">
         <v>1005.5</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="13">
         <v>796.5</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="13">
         <v>891.7</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="13">
         <v>771.7</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="13">
         <v>910.6</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4">
+      <c r="N3" s="13">
+        <f>+V3-SUM(K3:M3)</f>
+        <v>504.09999999999991</v>
+      </c>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13">
         <v>3418.4</v>
       </c>
-      <c r="U3" s="4">
+      <c r="U3" s="13">
         <v>3475.7</v>
       </c>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
+      <c r="V3" s="13">
+        <f>2204+874.1</f>
+        <v>3078.1</v>
+      </c>
+      <c r="W3" s="13"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
@@ -888,47 +921,53 @@
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4">
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13">
         <v>846</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="13">
         <v>790</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="13">
         <v>887.5</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="13">
         <v>872.2</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="13">
         <v>986.3</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="13">
         <v>753.7</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="13">
         <v>779.9</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="13">
         <v>678.1</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4">
+      <c r="N4" s="13">
+        <f t="shared" ref="N4:N21" si="0">+V4-SUM(K4:M4)</f>
+        <v>276.90000000000055</v>
+      </c>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13">
         <v>3389.9</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="13">
         <v>3536</v>
       </c>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
+      <c r="V4" s="13">
+        <f>1315.2+1173.4</f>
+        <v>2488.6000000000004</v>
+      </c>
+      <c r="W4" s="13"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
@@ -971,47 +1010,53 @@
       <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13">
         <v>468.3</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="13">
         <v>456.6</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="13">
         <v>411.9</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="13">
         <v>430.4</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="13">
         <v>506.6</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="13">
         <v>430.5</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="13">
         <v>390.5</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="13">
         <v>367.1</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4">
+      <c r="N5" s="13">
+        <f t="shared" si="0"/>
+        <v>518.09999999999991</v>
+      </c>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13">
         <v>1793.4</v>
       </c>
-      <c r="U5" s="4">
+      <c r="U5" s="13">
         <v>1805.5</v>
       </c>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
+      <c r="V5" s="13">
+        <f>488.4+750.8+467</f>
+        <v>1706.1999999999998</v>
+      </c>
+      <c r="W5" s="13"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
@@ -1054,47 +1099,52 @@
       <c r="B6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4">
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13">
         <v>1031.9000000000001</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="13">
         <v>1181.5</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="13">
         <v>1097</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="13">
         <v>1240.3</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="13">
         <v>1214.8</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="13">
         <v>1186</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="13">
         <v>1061.0999999999999</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="13">
         <v>1045.8</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4">
+      <c r="N6" s="13">
+        <f t="shared" si="0"/>
+        <v>820.80000000000018</v>
+      </c>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13">
         <v>4583.3999999999996</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="13">
         <v>4733.6000000000004</v>
       </c>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
+      <c r="V6" s="13">
+        <v>4113.7</v>
+      </c>
+      <c r="W6" s="13"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
@@ -1137,47 +1187,52 @@
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4">
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13">
         <v>657.4</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="13">
         <v>608.1</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="13">
         <v>705.6</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="13">
         <v>763.6</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="13">
         <v>736.5</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="13">
         <v>594.29999999999995</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="13">
         <v>597.79999999999995</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="13">
         <v>635.5</v>
       </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4">
+      <c r="N7" s="13">
+        <f t="shared" si="0"/>
+        <v>500.90000000000009</v>
+      </c>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13">
         <v>2763</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="13">
         <v>2813.9</v>
       </c>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
+      <c r="V7" s="13">
+        <v>2328.5</v>
+      </c>
+      <c r="W7" s="13"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
@@ -1220,47 +1275,52 @@
       <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13">
         <v>292.89999999999998</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="13">
         <v>312.7</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="13">
         <v>314.8</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="13">
         <v>304.2</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="13">
         <v>338</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="13">
         <v>295.7</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="13">
         <v>283.39999999999998</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="13">
         <v>274.39999999999998</v>
       </c>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4">
+      <c r="N8" s="13">
+        <f t="shared" si="0"/>
+        <v>0.40000000000009095</v>
+      </c>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13">
         <v>1255.3</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="13">
         <v>1269.7</v>
       </c>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
+      <c r="V8" s="13">
+        <v>853.9</v>
+      </c>
+      <c r="W8" s="13"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
@@ -1303,47 +1363,52 @@
       <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4">
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13">
         <v>1355</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="13">
         <v>1608.1</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="13">
         <v>1529.6</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="13">
         <v>1728.2</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="13">
         <v>1525.8</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="13">
         <v>1529.5</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="13">
         <v>1341.2</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="13">
         <v>1385.7</v>
       </c>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4">
+      <c r="N9" s="13">
+        <f t="shared" si="0"/>
+        <v>678.60000000000036</v>
+      </c>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13">
         <v>6468.7</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="13">
         <v>6391.8</v>
       </c>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
+      <c r="V9" s="13">
+        <v>4935</v>
+      </c>
+      <c r="W9" s="13"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
@@ -1386,47 +1451,52 @@
       <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4">
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13">
         <v>627.20000000000005</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="13">
         <v>494.2</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="13">
         <v>587.70000000000005</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="13">
         <v>580</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="13">
         <v>763.5</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="13">
         <v>546.5</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="13">
         <v>601.1</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10" s="13">
         <v>570</v>
       </c>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4">
+      <c r="N10" s="13">
+        <f t="shared" si="0"/>
+        <v>643.5</v>
+      </c>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13">
         <v>2133</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="13">
         <v>2425.4</v>
       </c>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
+      <c r="V10" s="13">
+        <v>2361.1</v>
+      </c>
+      <c r="W10" s="13"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
@@ -1469,49 +1539,54 @@
       <c r="B11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6">
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14">
         <v>2311.1</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="14">
         <v>1982.2</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="14">
         <v>2102.3000000000002</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="14">
         <v>2117.3000000000002</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="14">
         <v>2308.1999999999998</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="14">
         <v>2289.4</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="14">
         <v>2076</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="14">
         <v>1942.2</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="14">
         <v>1955.7</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="6">
+      <c r="N11" s="14">
+        <f t="shared" si="0"/>
+        <v>1322.3000000000002</v>
+      </c>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="14">
         <v>8601.7000000000007</v>
       </c>
-      <c r="U11" s="6">
+      <c r="U11" s="14">
         <v>8817.2000000000007</v>
       </c>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
+      <c r="V11" s="14">
+        <v>7296.2</v>
+      </c>
+      <c r="W11" s="13"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
@@ -1554,49 +1629,54 @@
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13">
         <v>1222.4000000000001</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="13">
         <v>1051.0999999999999</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="13">
         <v>1103.3</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="13">
         <v>1126.7</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="13">
         <v>1202.7</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="13">
         <v>1206.5</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="13">
         <v>1100.9000000000001</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="13">
         <v>1047.5999999999999</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M12" s="13">
         <v>1070.8</v>
       </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4">
+      <c r="N12" s="13">
+        <f t="shared" si="0"/>
+        <v>797.19999999999982</v>
+      </c>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13">
         <v>4615.1000000000004</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12" s="13">
         <v>4639.2</v>
       </c>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
+      <c r="V12" s="13">
+        <v>4016.5</v>
+      </c>
+      <c r="W12" s="13"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
@@ -1639,78 +1719,84 @@
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="4">
-        <f t="shared" ref="C13:H13" si="0">+C11-C12</f>
+      <c r="C13" s="13">
+        <f t="shared" ref="C13:H13" si="1">+C11-C12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="4">
-        <f t="shared" si="0"/>
+      <c r="D13" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E13" s="4">
-        <f t="shared" si="0"/>
+      <c r="E13" s="13">
+        <f t="shared" si="1"/>
         <v>1088.6999999999998</v>
       </c>
-      <c r="F13" s="4">
-        <f t="shared" si="0"/>
+      <c r="F13" s="13">
+        <f t="shared" si="1"/>
         <v>931.10000000000014</v>
       </c>
-      <c r="G13" s="4">
-        <f t="shared" si="0"/>
+      <c r="G13" s="13">
+        <f t="shared" si="1"/>
         <v>999.00000000000023</v>
       </c>
-      <c r="H13" s="4">
-        <f t="shared" si="0"/>
+      <c r="H13" s="13">
+        <f t="shared" si="1"/>
         <v>990.60000000000014</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="13">
         <f>+I11-I12</f>
         <v>1105.4999999999998</v>
       </c>
-      <c r="J13" s="4">
-        <f t="shared" ref="J13:M13" si="1">+J11-J12</f>
+      <c r="J13" s="13">
+        <f t="shared" ref="J13:N13" si="2">+J11-J12</f>
         <v>1082.9000000000001</v>
       </c>
-      <c r="K13" s="4">
-        <f t="shared" si="1"/>
+      <c r="K13" s="13">
+        <f t="shared" si="2"/>
         <v>975.09999999999991</v>
       </c>
-      <c r="L13" s="4">
-        <f t="shared" si="1"/>
+      <c r="L13" s="13">
+        <f t="shared" si="2"/>
         <v>894.60000000000014</v>
       </c>
-      <c r="M13" s="4">
-        <f t="shared" si="1"/>
+      <c r="M13" s="13">
+        <f t="shared" si="2"/>
         <v>884.90000000000009</v>
       </c>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4">
-        <f t="shared" ref="P13:T13" si="2">+P11-P12</f>
+      <c r="N13" s="13">
+        <f t="shared" si="2"/>
+        <v>525.10000000000036</v>
+      </c>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13">
+        <f t="shared" ref="P13:T13" si="3">+P11-P12</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="4">
-        <f t="shared" si="2"/>
+      <c r="Q13" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R13" s="4">
-        <f t="shared" si="2"/>
+      <c r="R13" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S13" s="4">
-        <f t="shared" si="2"/>
+      <c r="S13" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T13" s="4">
-        <f t="shared" si="2"/>
+      <c r="T13" s="13">
+        <f t="shared" si="3"/>
         <v>3986.6000000000004</v>
       </c>
-      <c r="U13" s="4">
+      <c r="U13" s="13">
         <f>+U11-U12</f>
         <v>4178.0000000000009</v>
       </c>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
+      <c r="V13" s="13">
+        <f>+V11-V12</f>
+        <v>3279.7</v>
+      </c>
+      <c r="W13" s="13"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
@@ -1753,49 +1839,54 @@
       <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13">
         <v>11.3</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="13">
         <v>11.3</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="13">
         <v>5.2</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="13">
         <v>5.9</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="13">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="13">
         <v>8.1999999999999993</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="13">
         <v>5.5</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="13">
         <v>6.9</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M14" s="13">
         <v>5.2</v>
       </c>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4">
+      <c r="N14" s="13">
+        <f t="shared" si="0"/>
+        <v>74.800000000000011</v>
+      </c>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13">
         <v>38.5</v>
       </c>
-      <c r="U14" s="4">
+      <c r="U14" s="13">
         <v>24.3</v>
       </c>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
+      <c r="V14" s="13">
+        <v>92.4</v>
+      </c>
+      <c r="W14" s="13"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
@@ -1838,51 +1929,57 @@
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13">
         <v>863.7</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="13">
         <v>848</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="13">
         <v>845.3</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="13">
         <v>879.3</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="13">
         <v>873.4</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="13">
         <v>982.2</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="13">
         <f>904.9+18</f>
         <v>922.9</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="13">
         <v>914.7</v>
       </c>
-      <c r="M15" s="4">
+      <c r="M15" s="13">
         <f>850.6+10.1</f>
         <v>860.7</v>
       </c>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4">
+      <c r="N15" s="13">
+        <f t="shared" si="0"/>
+        <v>1030.9999999999995</v>
+      </c>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13">
         <v>3403.5</v>
       </c>
-      <c r="U15" s="4">
+      <c r="U15" s="13">
         <v>3580.2</v>
       </c>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
+      <c r="V15" s="13">
+        <f>3537.7+191.6</f>
+        <v>3729.2999999999997</v>
+      </c>
+      <c r="W15" s="13"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
@@ -1925,78 +2022,84 @@
       <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="4">
-        <f t="shared" ref="C16:H16" si="3">+C13+C14-C15</f>
+      <c r="C16" s="13">
+        <f t="shared" ref="C16:H16" si="4">+C13+C14-C15</f>
         <v>0</v>
       </c>
-      <c r="D16" s="4">
-        <f t="shared" si="3"/>
+      <c r="D16" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E16" s="4">
-        <f t="shared" si="3"/>
+      <c r="E16" s="13">
+        <f t="shared" si="4"/>
         <v>236.29999999999973</v>
       </c>
-      <c r="F16" s="4">
-        <f t="shared" si="3"/>
+      <c r="F16" s="13">
+        <f t="shared" si="4"/>
         <v>94.400000000000091</v>
       </c>
-      <c r="G16" s="4">
-        <f t="shared" si="3"/>
+      <c r="G16" s="13">
+        <f t="shared" si="4"/>
         <v>158.90000000000032</v>
       </c>
-      <c r="H16" s="4">
-        <f t="shared" si="3"/>
+      <c r="H16" s="13">
+        <f t="shared" si="4"/>
         <v>117.20000000000016</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="13">
         <f>+I13+I14-I15</f>
         <v>236.99999999999989</v>
       </c>
-      <c r="J16" s="4">
-        <f t="shared" ref="J16:M16" si="4">+J13+J14-J15</f>
+      <c r="J16" s="13">
+        <f t="shared" ref="J16:N16" si="5">+J13+J14-J15</f>
         <v>108.90000000000009</v>
       </c>
-      <c r="K16" s="4">
-        <f t="shared" si="4"/>
+      <c r="K16" s="13">
+        <f t="shared" si="5"/>
         <v>57.699999999999932</v>
       </c>
-      <c r="L16" s="4">
-        <f t="shared" si="4"/>
+      <c r="L16" s="13">
+        <f t="shared" si="5"/>
         <v>-13.199999999999932</v>
       </c>
-      <c r="M16" s="4">
-        <f t="shared" si="4"/>
+      <c r="M16" s="13">
+        <f t="shared" si="5"/>
         <v>29.400000000000091</v>
       </c>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4">
-        <f t="shared" ref="P16:T16" si="5">+P13+P14-P15</f>
+      <c r="N16" s="13">
+        <f t="shared" si="5"/>
+        <v>-431.09999999999923</v>
+      </c>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13">
+        <f t="shared" ref="P16:T16" si="6">+P13+P14-P15</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="4">
-        <f t="shared" si="5"/>
+      <c r="Q16" s="13">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R16" s="4">
-        <f t="shared" si="5"/>
+      <c r="R16" s="13">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S16" s="4">
-        <f t="shared" si="5"/>
+      <c r="S16" s="13">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T16" s="4">
-        <f t="shared" si="5"/>
+      <c r="T16" s="13">
+        <f t="shared" si="6"/>
         <v>621.60000000000036</v>
       </c>
-      <c r="U16" s="4">
+      <c r="U16" s="13">
         <f>+U13+U14-U15</f>
         <v>622.10000000000127</v>
       </c>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
+      <c r="V16" s="13">
+        <f>+V13+V14-V15</f>
+        <v>-357.19999999999982</v>
+      </c>
+      <c r="W16" s="13"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
@@ -2039,50 +2142,55 @@
       <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13">
         <v>45.5</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="13">
         <v>67.099999999999994</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="13">
         <v>26.8</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="13">
         <v>42.6</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="13">
         <v>46.7</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="13">
         <v>43.5</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="13">
         <v>42</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="13">
         <f>84.6+46.6</f>
         <v>131.19999999999999</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M17" s="13">
         <v>43.8</v>
       </c>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4">
+      <c r="N17" s="13">
+        <f t="shared" si="0"/>
+        <v>-51.300000000000011</v>
+      </c>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13">
         <v>143.30000000000001</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17" s="13">
         <v>159.69999999999999</v>
       </c>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
+      <c r="V17" s="13">
+        <v>165.7</v>
+      </c>
+      <c r="W17" s="13"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
@@ -2125,78 +2233,84 @@
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="4">
-        <f t="shared" ref="C18:D18" si="6">+C16-C17</f>
+      <c r="C18" s="13">
+        <f t="shared" ref="C18:D18" si="7">+C16-C17</f>
         <v>0</v>
       </c>
-      <c r="D18" s="4">
-        <f t="shared" si="6"/>
+      <c r="D18" s="13">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="13">
         <f>+E16-E17</f>
         <v>190.79999999999973</v>
       </c>
-      <c r="F18" s="4">
-        <f t="shared" ref="F18:M18" si="7">+F16-F17</f>
+      <c r="F18" s="13">
+        <f t="shared" ref="F18:N18" si="8">+F16-F17</f>
         <v>27.300000000000097</v>
       </c>
-      <c r="G18" s="4">
-        <f t="shared" si="7"/>
+      <c r="G18" s="13">
+        <f t="shared" si="8"/>
         <v>132.10000000000031</v>
       </c>
-      <c r="H18" s="4">
-        <f t="shared" si="7"/>
+      <c r="H18" s="13">
+        <f t="shared" si="8"/>
         <v>74.600000000000165</v>
       </c>
-      <c r="I18" s="4">
-        <f t="shared" si="7"/>
+      <c r="I18" s="13">
+        <f t="shared" si="8"/>
         <v>190.2999999999999</v>
       </c>
-      <c r="J18" s="4">
-        <f t="shared" si="7"/>
+      <c r="J18" s="13">
+        <f t="shared" si="8"/>
         <v>65.400000000000091</v>
       </c>
-      <c r="K18" s="4">
-        <f t="shared" si="7"/>
+      <c r="K18" s="13">
+        <f t="shared" si="8"/>
         <v>15.699999999999932</v>
       </c>
-      <c r="L18" s="4">
-        <f t="shared" si="7"/>
+      <c r="L18" s="13">
+        <f t="shared" si="8"/>
         <v>-144.39999999999992</v>
       </c>
-      <c r="M18" s="4">
-        <f t="shared" si="7"/>
+      <c r="M18" s="13">
+        <f t="shared" si="8"/>
         <v>-14.399999999999906</v>
       </c>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4">
-        <f t="shared" ref="P18:T18" si="8">+P16-P17</f>
+      <c r="N18" s="13">
+        <f t="shared" si="8"/>
+        <v>-379.79999999999922</v>
+      </c>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13">
+        <f t="shared" ref="P18:T18" si="9">+P16-P17</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="4">
-        <f t="shared" si="8"/>
+      <c r="Q18" s="13">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R18" s="4">
-        <f t="shared" si="8"/>
+      <c r="R18" s="13">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S18" s="4">
-        <f t="shared" si="8"/>
+      <c r="S18" s="13">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T18" s="4">
-        <f t="shared" si="8"/>
+      <c r="T18" s="13">
+        <f t="shared" si="9"/>
         <v>478.30000000000035</v>
       </c>
-      <c r="U18" s="4">
+      <c r="U18" s="13">
         <f>+U16-U17</f>
         <v>462.40000000000128</v>
       </c>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
+      <c r="V18" s="13">
+        <f>+V16-V17</f>
+        <v>-522.89999999999986</v>
+      </c>
+      <c r="W18" s="13"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
@@ -2239,49 +2353,54 @@
       <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4">
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13">
         <v>47.9</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="13">
         <v>4.9000000000000004</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="13">
         <v>33</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="13">
         <v>18.399999999999999</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="13">
         <v>47.8</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="13">
         <v>20.7</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="13">
         <v>4.2</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="13">
         <v>94.7</v>
       </c>
-      <c r="M19" s="4">
+      <c r="M19" s="13">
         <v>37.9</v>
       </c>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4">
+      <c r="N19" s="13">
+        <f t="shared" si="0"/>
+        <v>-16.100000000000009</v>
+      </c>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13">
         <v>117.8</v>
       </c>
-      <c r="U19" s="4">
+      <c r="U19" s="13">
         <v>120</v>
       </c>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
+      <c r="V19" s="13">
+        <v>120.7</v>
+      </c>
+      <c r="W19" s="13"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
@@ -2324,78 +2443,84 @@
       <c r="B20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="4">
-        <f t="shared" ref="C20:D20" si="9">+C18-C19</f>
+      <c r="C20" s="13">
+        <f t="shared" ref="C20:D20" si="10">+C18-C19</f>
         <v>0</v>
       </c>
-      <c r="D20" s="4">
-        <f t="shared" si="9"/>
+      <c r="D20" s="13">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="13">
         <f>+E18-E19</f>
         <v>142.89999999999972</v>
       </c>
-      <c r="F20" s="4">
-        <f t="shared" ref="F20:M20" si="10">+F18-F19</f>
+      <c r="F20" s="13">
+        <f t="shared" ref="F20:N20" si="11">+F18-F19</f>
         <v>22.400000000000098</v>
       </c>
-      <c r="G20" s="4">
-        <f t="shared" si="10"/>
+      <c r="G20" s="13">
+        <f t="shared" si="11"/>
         <v>99.100000000000307</v>
       </c>
-      <c r="H20" s="4">
-        <f t="shared" si="10"/>
+      <c r="H20" s="13">
+        <f t="shared" si="11"/>
         <v>56.200000000000166</v>
       </c>
-      <c r="I20" s="4">
-        <f t="shared" si="10"/>
+      <c r="I20" s="13">
+        <f t="shared" si="11"/>
         <v>142.49999999999989</v>
       </c>
-      <c r="J20" s="4">
-        <f t="shared" si="10"/>
+      <c r="J20" s="13">
+        <f t="shared" si="11"/>
         <v>44.700000000000088</v>
       </c>
-      <c r="K20" s="4">
-        <f t="shared" si="10"/>
+      <c r="K20" s="13">
+        <f t="shared" si="11"/>
         <v>11.499999999999932</v>
       </c>
-      <c r="L20" s="4">
-        <f t="shared" si="10"/>
+      <c r="L20" s="13">
+        <f t="shared" si="11"/>
         <v>-239.09999999999991</v>
       </c>
-      <c r="M20" s="4">
-        <f t="shared" si="10"/>
+      <c r="M20" s="13">
+        <f t="shared" si="11"/>
         <v>-52.299999999999905</v>
       </c>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4">
-        <f t="shared" ref="P20:T20" si="11">+P18-P19</f>
+      <c r="N20" s="13">
+        <f t="shared" si="11"/>
+        <v>-363.69999999999919</v>
+      </c>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13">
+        <f t="shared" ref="P20:T20" si="12">+P18-P19</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="4">
-        <f t="shared" si="11"/>
+      <c r="Q20" s="13">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R20" s="4">
-        <f t="shared" si="11"/>
+      <c r="R20" s="13">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S20" s="4">
-        <f t="shared" si="11"/>
+      <c r="S20" s="13">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T20" s="4">
-        <f t="shared" si="11"/>
+      <c r="T20" s="13">
+        <f t="shared" si="12"/>
         <v>360.50000000000034</v>
       </c>
-      <c r="U20" s="4">
+      <c r="U20" s="13">
         <f>+U18-U19</f>
         <v>342.40000000000128</v>
       </c>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
+      <c r="V20" s="13">
+        <f>+V18-V19</f>
+        <v>-643.59999999999991</v>
+      </c>
+      <c r="W20" s="13"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
@@ -2438,49 +2563,55 @@
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4">
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13">
         <v>11.3</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="13">
         <v>21.6</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="13">
         <v>11.8</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="13">
         <v>14.3</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="13">
         <v>14.6</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="13">
         <v>20.100000000000001</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="13">
         <v>11.1</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="13">
         <v>7.9</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M21" s="13">
         <v>10</v>
       </c>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4">
+      <c r="N21" s="13">
+        <f t="shared" si="0"/>
+        <v>-27.099999999999998</v>
+      </c>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13">
         <v>55.7</v>
       </c>
-      <c r="U21" s="4">
+      <c r="U21" s="13">
         <v>60.7</v>
       </c>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
+      <c r="V21" s="13">
+        <f>30.3-28.4</f>
+        <v>1.9000000000000021</v>
+      </c>
+      <c r="W21" s="13"/>
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
@@ -2523,78 +2654,84 @@
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="4">
-        <f t="shared" ref="C22:D22" si="12">+C20-C21</f>
+      <c r="C22" s="13">
+        <f t="shared" ref="C22:D22" si="13">+C20-C21</f>
         <v>0</v>
       </c>
-      <c r="D22" s="4">
-        <f t="shared" si="12"/>
+      <c r="D22" s="13">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="13">
         <f>+E20-E21</f>
         <v>131.59999999999971</v>
       </c>
-      <c r="F22" s="4">
-        <f t="shared" ref="F22:M22" si="13">+F20-F21</f>
+      <c r="F22" s="13">
+        <f t="shared" ref="F22:N22" si="14">+F20-F21</f>
         <v>0.80000000000009663</v>
       </c>
-      <c r="G22" s="4">
-        <f t="shared" si="13"/>
+      <c r="G22" s="13">
+        <f t="shared" si="14"/>
         <v>87.30000000000031</v>
       </c>
-      <c r="H22" s="4">
-        <f t="shared" si="13"/>
+      <c r="H22" s="13">
+        <f t="shared" si="14"/>
         <v>41.900000000000162</v>
       </c>
-      <c r="I22" s="4">
-        <f t="shared" si="13"/>
+      <c r="I22" s="13">
+        <f t="shared" si="14"/>
         <v>127.89999999999989</v>
       </c>
-      <c r="J22" s="4">
-        <f t="shared" si="13"/>
+      <c r="J22" s="13">
+        <f t="shared" si="14"/>
         <v>24.600000000000087</v>
       </c>
-      <c r="K22" s="4">
-        <f t="shared" si="13"/>
+      <c r="K22" s="13">
+        <f t="shared" si="14"/>
         <v>0.39999999999993285</v>
       </c>
-      <c r="L22" s="4">
-        <f t="shared" si="13"/>
+      <c r="L22" s="13">
+        <f t="shared" si="14"/>
         <v>-246.99999999999991</v>
       </c>
-      <c r="M22" s="4">
-        <f t="shared" si="13"/>
+      <c r="M22" s="13">
+        <f t="shared" si="14"/>
         <v>-62.299999999999905</v>
       </c>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4">
-        <f t="shared" ref="P22:T22" si="14">+P20-P21</f>
+      <c r="N22" s="13">
+        <f t="shared" si="14"/>
+        <v>-336.59999999999917</v>
+      </c>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13">
+        <f t="shared" ref="P22:T22" si="15">+P20-P21</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="4">
-        <f t="shared" si="14"/>
+      <c r="Q22" s="13">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="R22" s="4">
-        <f t="shared" si="14"/>
+      <c r="R22" s="13">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="S22" s="4">
-        <f t="shared" si="14"/>
+      <c r="S22" s="13">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="T22" s="4">
-        <f t="shared" si="14"/>
+      <c r="T22" s="13">
+        <f t="shared" si="15"/>
         <v>304.80000000000035</v>
       </c>
-      <c r="U22" s="4">
+      <c r="U22" s="13">
         <f>+U20-U21</f>
         <v>281.7000000000013</v>
       </c>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
+      <c r="V22" s="13">
+        <f>+V20-V21</f>
+        <v>-645.49999999999989</v>
+      </c>
+      <c r="W22" s="13"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
@@ -2698,11 +2835,11 @@
         <v>30</v>
       </c>
       <c r="C24" s="7" t="e">
-        <f t="shared" ref="C24:D24" si="15">+C22/C25</f>
+        <f t="shared" ref="C24:D24" si="16">+C22/C25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D24" s="7" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E24" s="7">
@@ -2710,53 +2847,56 @@
         <v>0.87838739821118483</v>
       </c>
       <c r="F24" s="7">
-        <f t="shared" ref="F24:M24" si="16">+F22/F25</f>
+        <f t="shared" ref="F24:N24" si="17">+F22/F25</f>
         <v>5.3386720053393167E-3</v>
       </c>
       <c r="G24" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.58231056563500749</v>
       </c>
       <c r="H24" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.27973192148337656</v>
       </c>
       <c r="I24" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.85557562378754359</v>
       </c>
       <c r="J24" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.16474685239753609</v>
       </c>
       <c r="K24" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.7012425715824745E-3</v>
       </c>
       <c r="L24" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1.6732199307509137</v>
       </c>
       <c r="M24" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-0.4224588051807141</v>
       </c>
-      <c r="N24" s="7"/>
+      <c r="N24" s="7">
+        <f t="shared" si="17"/>
+        <v>-2.2824981352139364</v>
+      </c>
       <c r="O24" s="4"/>
       <c r="P24" s="7" t="e">
-        <f t="shared" ref="P24:S24" si="17">+P22/P25</f>
+        <f t="shared" ref="P24:S24" si="18">+P22/P25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q24" s="7" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R24" s="7" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S24" s="7" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T24" s="7">
@@ -2764,10 +2904,13 @@
         <v>2.0340340340340366</v>
       </c>
       <c r="U24" s="7">
-        <f t="shared" ref="U24" si="18">+U22/U25</f>
+        <f t="shared" ref="U24:V24" si="19">+U22/U25</f>
         <v>1.886552370747397</v>
       </c>
-      <c r="V24" s="4"/>
+      <c r="V24" s="7">
+        <f t="shared" si="19"/>
+        <v>-4.3789430839156092</v>
+      </c>
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
@@ -2840,7 +2983,9 @@
       <c r="M25" s="4">
         <v>147.47</v>
       </c>
-      <c r="N25" s="4"/>
+      <c r="N25" s="4">
+        <v>147.47</v>
+      </c>
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
@@ -2852,7 +2997,9 @@
       <c r="U25" s="4">
         <v>149.32</v>
       </c>
-      <c r="V25" s="4"/>
+      <c r="V25" s="4">
+        <v>147.41</v>
+      </c>
       <c r="W25" s="4"/>
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
@@ -2971,18 +3118,21 @@
         <v>0.15497931591161329</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" ref="K27:M27" si="19">+K11/G11-1</f>
+        <f t="shared" ref="K27:N27" si="20">+K11/G11-1</f>
         <v>-1.2510107976977713E-2</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-8.2699664667264972E-2</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.15271640239147377</v>
       </c>
-      <c r="N27" s="8"/>
+      <c r="N27" s="8">
+        <f t="shared" si="20"/>
+        <v>-0.42242508954311164</v>
+      </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
       <c r="Q27" s="6"/>
@@ -3035,27 +3185,27 @@
         <v>32</v>
       </c>
       <c r="C28" s="9" t="e">
-        <f t="shared" ref="C28:H28" si="20">+C13/C11</f>
+        <f t="shared" ref="C28:H28" si="21">+C13/C11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="9" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.47107438016528919</v>
       </c>
       <c r="F28" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.46973060236101305</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.47519383532321752</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.46786001039059183</v>
       </c>
       <c r="I28" s="9">
@@ -3063,22 +3213,25 @@
         <v>0.47894463218092015</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" ref="J28:K28" si="21">+J13/J11</f>
+        <f t="shared" ref="J28:K28" si="22">+J13/J11</f>
         <v>0.47300602778020445</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.46970134874759145</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" ref="L28:M28" si="22">+L13/L11</f>
+        <f t="shared" ref="L28:M28" si="23">+L13/L11</f>
         <v>0.46061167747914744</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.45247226057166234</v>
       </c>
-      <c r="N28" s="9"/>
+      <c r="N28" s="9">
+        <f t="shared" ref="N28" si="24">+N13/N11</f>
+        <v>0.39711109430537722</v>
+      </c>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
@@ -3131,27 +3284,27 @@
         <v>33</v>
       </c>
       <c r="C29" s="9" t="e">
-        <f t="shared" ref="C29:H29" si="23">+C16/C11</f>
+        <f t="shared" ref="C29:H29" si="25">+C16/C11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="9" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.10224568387348004</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>4.7623852285339566E-2</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7.5583884317176567E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>5.5353516270722214E-2</v>
       </c>
       <c r="I29" s="9">
@@ -3159,22 +3312,25 @@
         <v>0.10267741096958664</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" ref="J29:K29" si="24">+J16/J11</f>
+        <f t="shared" ref="J29:K29" si="26">+J16/J11</f>
         <v>4.7567048134882536E-2</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>2.7793834296724437E-2</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" ref="L29:M29" si="25">+L16/L11</f>
+        <f t="shared" ref="L29:M29" si="27">+L16/L11</f>
         <v>-6.7964164349706164E-3</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.5032980518484475E-2</v>
       </c>
-      <c r="N29" s="9"/>
+      <c r="N29" s="9">
+        <f t="shared" ref="N29" si="28">+N16/N11</f>
+        <v>-0.32602283899266365</v>
+      </c>
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
@@ -3227,27 +3383,27 @@
         <v>34</v>
       </c>
       <c r="C30" s="9" t="e">
-        <f t="shared" ref="C30:H30" si="26">+C19/C18</f>
+        <f t="shared" ref="C30:H30" si="29">+C19/C18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D30" s="9" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.25104821802935046</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.17948717948717888</v>
       </c>
       <c r="G30" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.24981074943224771</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.24664879356568309</v>
       </c>
       <c r="I30" s="9">
@@ -3255,22 +3411,25 @@
         <v>0.25118234366789294</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" ref="J30:K30" si="27">+J19/J18</f>
+        <f t="shared" ref="J30:K30" si="30">+J19/J18</f>
         <v>0.31651376146788945</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.26751592356688014</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" ref="L30:M30" si="28">+L19/L18</f>
+        <f t="shared" ref="L30:M30" si="31">+L19/L18</f>
         <v>-0.6558171745152358</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>-2.6319444444444615</v>
       </c>
-      <c r="N30" s="9"/>
+      <c r="N30" s="9">
+        <f t="shared" ref="N30" si="32">+N19/N18</f>
+        <v>4.239073196419179E-2</v>
+      </c>
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>

--- a/PUM.DE.xlsx
+++ b/PUM.DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA2B566-5B9B-4899-97E8-6C276AE17A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8323A2FA-6EE3-4458-8BC1-B56197884B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{DF056538-1695-47DF-BC32-BA7DD1F9A83B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{DF056538-1695-47DF-BC32-BA7DD1F9A83B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t xml:space="preserve">Puma </t>
   </si>
@@ -209,6 +209,18 @@
   <si>
     <t>Arthur Hoeld</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -218,13 +230,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -293,31 +311,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -674,7 +692,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>24.05</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -682,10 +700,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="4">
-        <v>147.41</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>52</v>
+        <v>147.22999999999999</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -697,7 +715,7 @@
       </c>
       <c r="I4" s="4">
         <f>+I2*I3</f>
-        <v>3545.2105000000001</v>
+        <v>3825.0353999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -708,10 +726,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="4">
-        <v>290</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>52</v>
+        <v>326.2</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -719,11 +737,11 @@
         <v>6</v>
       </c>
       <c r="I6" s="4">
-        <f>424.2+144.1+3.7</f>
-        <v>572</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>52</v>
+        <f>1139.8+544</f>
+        <v>1683.8</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -732,17 +750,17 @@
       </c>
       <c r="I7" s="4">
         <f>+I4-I5+I6</f>
-        <v>3827.2105000000001</v>
+        <v>5182.6354000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="I8" s="4"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="11" t="s">
         <v>56</v>
       </c>
     </row>
@@ -756,7 +774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358FBAD2-1CB2-460A-BF2B-D7C2BA58E00E}">
-  <dimension ref="A1:BH264"/>
+  <dimension ref="A1:BL264"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -764,12 +782,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:64" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
@@ -806,83 +824,97 @@
       <c r="N2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="Y2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="Z2" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12">
         <v>667.9</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>855.7</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <v>817.9</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="12">
         <v>1005.5</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="12">
         <v>796.5</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="12">
         <v>891.7</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="12">
         <v>771.7</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="12">
         <v>910.6</v>
       </c>
-      <c r="N3" s="13">
-        <f>+V3-SUM(K3:M3)</f>
+      <c r="N3" s="12">
+        <f>+Z3-SUM(K3:M3)</f>
         <v>504.09999999999991</v>
       </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13">
+      <c r="O3" s="12">
+        <v>774.5</v>
+      </c>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12">
         <v>3418.4</v>
       </c>
-      <c r="U3" s="13">
+      <c r="Y3" s="12">
         <v>3475.7</v>
       </c>
-      <c r="V3" s="13">
+      <c r="Z3" s="12">
         <f>2204+874.1</f>
         <v>3078.1</v>
       </c>
-      <c r="W3" s="13"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="AA3" s="12"/>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
@@ -916,62 +948,68 @@
       <c r="BF3" s="4"/>
       <c r="BG3" s="4"/>
       <c r="BH3" s="4"/>
-    </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI3" s="4"/>
+      <c r="BJ3" s="4"/>
+      <c r="BK3" s="4"/>
+      <c r="BL3" s="4"/>
+    </row>
+    <row r="4" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12">
         <v>846</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>790</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>887.5</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <v>872.2</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <v>986.3</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="12">
         <v>753.7</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <v>779.9</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="12">
         <v>678.1</v>
       </c>
-      <c r="N4" s="13">
-        <f t="shared" ref="N4:N21" si="0">+V4-SUM(K4:M4)</f>
+      <c r="N4" s="12">
+        <f t="shared" ref="N4:N21" si="0">+Z4-SUM(K4:M4)</f>
         <v>276.90000000000055</v>
       </c>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13">
+      <c r="O4" s="12">
+        <v>655.6</v>
+      </c>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12">
         <v>3389.9</v>
       </c>
-      <c r="U4" s="13">
+      <c r="Y4" s="12">
         <v>3536</v>
       </c>
-      <c r="V4" s="13">
+      <c r="Z4" s="12">
         <f>1315.2+1173.4</f>
         <v>2488.6000000000004</v>
       </c>
-      <c r="W4" s="13"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="AA4" s="12"/>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
@@ -1005,62 +1043,68 @@
       <c r="BF4" s="4"/>
       <c r="BG4" s="4"/>
       <c r="BH4" s="4"/>
-    </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI4" s="4"/>
+      <c r="BJ4" s="4"/>
+      <c r="BK4" s="4"/>
+      <c r="BL4" s="4"/>
+    </row>
+    <row r="5" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12">
         <v>468.3</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>456.6</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <v>411.9</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <v>430.4</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <v>506.6</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <v>430.5</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <v>390.5</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <v>367.1</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <f t="shared" si="0"/>
         <v>518.09999999999991</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13">
+      <c r="O5" s="12">
+        <v>433.8</v>
+      </c>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12">
         <v>1793.4</v>
       </c>
-      <c r="U5" s="13">
+      <c r="Y5" s="12">
         <v>1805.5</v>
       </c>
-      <c r="V5" s="13">
+      <c r="Z5" s="12">
         <f>488.4+750.8+467</f>
         <v>1706.1999999999998</v>
       </c>
-      <c r="W5" s="13"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="AA5" s="12"/>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
@@ -1094,61 +1138,67 @@
       <c r="BF5" s="4"/>
       <c r="BG5" s="4"/>
       <c r="BH5" s="4"/>
-    </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI5" s="4"/>
+      <c r="BJ5" s="4"/>
+      <c r="BK5" s="4"/>
+      <c r="BL5" s="4"/>
+    </row>
+    <row r="6" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13">
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12">
         <v>1031.9000000000001</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>1181.5</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <v>1097</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <v>1240.3</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <v>1214.8</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <v>1186</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="12">
         <v>1061.0999999999999</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="12">
         <v>1045.8</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="12">
         <f t="shared" si="0"/>
         <v>820.80000000000018</v>
       </c>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13">
+      <c r="O6" s="12">
+        <v>1089.5999999999999</v>
+      </c>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12">
         <v>4583.3999999999996</v>
       </c>
-      <c r="U6" s="13">
+      <c r="Y6" s="12">
         <v>4733.6000000000004</v>
       </c>
-      <c r="V6" s="13">
+      <c r="Z6" s="12">
         <v>4113.7</v>
       </c>
-      <c r="W6" s="13"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="AA6" s="12"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
@@ -1182,61 +1232,67 @@
       <c r="BF6" s="4"/>
       <c r="BG6" s="4"/>
       <c r="BH6" s="4"/>
-    </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI6" s="4"/>
+      <c r="BJ6" s="4"/>
+      <c r="BK6" s="4"/>
+      <c r="BL6" s="4"/>
+    </row>
+    <row r="7" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13">
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12">
         <v>657.4</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>608.1</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <v>705.6</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <v>763.6</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="12">
         <v>736.5</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="12">
         <v>594.29999999999995</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="12">
         <v>597.79999999999995</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="12">
         <v>635.5</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="12">
         <f t="shared" si="0"/>
         <v>500.90000000000009</v>
       </c>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13">
+      <c r="O7" s="12">
+        <v>546.29999999999995</v>
+      </c>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12">
         <v>2763</v>
       </c>
-      <c r="U7" s="13">
+      <c r="Y7" s="12">
         <v>2813.9</v>
       </c>
-      <c r="V7" s="13">
+      <c r="Z7" s="12">
         <v>2328.5</v>
       </c>
-      <c r="W7" s="13"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="AA7" s="12"/>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
@@ -1270,61 +1326,67 @@
       <c r="BF7" s="4"/>
       <c r="BG7" s="4"/>
       <c r="BH7" s="4"/>
-    </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI7" s="4"/>
+      <c r="BJ7" s="4"/>
+      <c r="BK7" s="4"/>
+      <c r="BL7" s="4"/>
+    </row>
+    <row r="8" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13">
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12">
         <v>292.89999999999998</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>312.7</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <v>314.8</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <v>304.2</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <v>338</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="12">
         <v>295.7</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="12">
         <v>283.39999999999998</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="12">
         <v>274.39999999999998</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="12">
         <f t="shared" si="0"/>
         <v>0.40000000000009095</v>
       </c>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13">
+      <c r="O8" s="12">
+        <v>227.9</v>
+      </c>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12">
         <v>1255.3</v>
       </c>
-      <c r="U8" s="13">
+      <c r="Y8" s="12">
         <v>1269.7</v>
       </c>
-      <c r="V8" s="13">
+      <c r="Z8" s="12">
         <v>853.9</v>
       </c>
-      <c r="W8" s="13"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
+      <c r="AA8" s="12"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
@@ -1358,61 +1420,67 @@
       <c r="BF8" s="4"/>
       <c r="BG8" s="4"/>
       <c r="BH8" s="4"/>
-    </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI8" s="4"/>
+      <c r="BJ8" s="4"/>
+      <c r="BK8" s="4"/>
+      <c r="BL8" s="4"/>
+    </row>
+    <row r="9" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13">
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12">
         <v>1355</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>1608.1</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <v>1529.6</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <v>1728.2</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <v>1525.8</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="12">
         <v>1529.5</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="12">
         <v>1341.2</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="12">
         <v>1385.7</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="12">
         <f t="shared" si="0"/>
         <v>678.60000000000036</v>
       </c>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13">
+      <c r="O9" s="12">
+        <v>1335.7</v>
+      </c>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12">
         <v>6468.7</v>
       </c>
-      <c r="U9" s="13">
+      <c r="Y9" s="12">
         <v>6391.8</v>
       </c>
-      <c r="V9" s="13">
+      <c r="Z9" s="12">
         <v>4935</v>
       </c>
-      <c r="W9" s="13"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
+      <c r="AA9" s="12"/>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
@@ -1446,61 +1514,67 @@
       <c r="BF9" s="4"/>
       <c r="BG9" s="4"/>
       <c r="BH9" s="4"/>
-    </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI9" s="4"/>
+      <c r="BJ9" s="4"/>
+      <c r="BK9" s="4"/>
+      <c r="BL9" s="4"/>
+    </row>
+    <row r="10" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12">
         <v>627.20000000000005</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <v>494.2</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <v>587.70000000000005</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <v>580</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="12">
         <v>763.5</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="12">
         <v>546.5</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="12">
         <v>601.1</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="12">
         <v>570</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="12">
         <f t="shared" si="0"/>
         <v>643.5</v>
       </c>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13">
+      <c r="O10" s="12">
+        <v>528.1</v>
+      </c>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12">
         <v>2133</v>
       </c>
-      <c r="U10" s="13">
+      <c r="Y10" s="12">
         <v>2425.4</v>
       </c>
-      <c r="V10" s="13">
+      <c r="Z10" s="12">
         <v>2361.1</v>
       </c>
-      <c r="W10" s="13"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
+      <c r="AA10" s="12"/>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
@@ -1534,63 +1608,69 @@
       <c r="BF10" s="4"/>
       <c r="BG10" s="4"/>
       <c r="BH10" s="4"/>
-    </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI10" s="4"/>
+      <c r="BJ10" s="4"/>
+      <c r="BK10" s="4"/>
+      <c r="BL10" s="4"/>
+    </row>
+    <row r="11" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13">
         <v>2311.1</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="13">
         <v>1982.2</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <v>2102.3000000000002</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>2117.3000000000002</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>2308.1999999999998</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <v>2289.4</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>2076</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="13">
         <v>1942.2</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="13">
         <v>1955.7</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="13">
         <f t="shared" si="0"/>
         <v>1322.3000000000002</v>
       </c>
-      <c r="O11" s="13"/>
+      <c r="O11" s="13">
+        <v>1863.8</v>
+      </c>
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="14">
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="13">
         <v>8601.7000000000007</v>
       </c>
-      <c r="U11" s="14">
+      <c r="Y11" s="13">
         <v>8817.2000000000007</v>
       </c>
-      <c r="V11" s="14">
+      <c r="Z11" s="13">
         <v>7296.2</v>
       </c>
-      <c r="W11" s="13"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
+      <c r="AA11" s="12"/>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
@@ -1624,63 +1704,69 @@
       <c r="BF11" s="4"/>
       <c r="BG11" s="4"/>
       <c r="BH11" s="4"/>
-    </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI11" s="4"/>
+      <c r="BJ11" s="4"/>
+      <c r="BK11" s="4"/>
+      <c r="BL11" s="4"/>
+    </row>
+    <row r="12" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13">
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12">
         <v>1222.4000000000001</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>1051.0999999999999</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <v>1103.3</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <v>1126.7</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <v>1202.7</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="12">
         <v>1206.5</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="12">
         <v>1100.9000000000001</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="12">
         <v>1047.5999999999999</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="12">
         <v>1070.8</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="12">
         <f t="shared" si="0"/>
         <v>797.19999999999982</v>
       </c>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13">
+      <c r="O12" s="12">
+        <v>974.9</v>
+      </c>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="12">
         <v>4615.1000000000004</v>
       </c>
-      <c r="U12" s="13">
+      <c r="Y12" s="12">
         <v>4639.2</v>
       </c>
-      <c r="V12" s="13">
+      <c r="Z12" s="12">
         <v>4016.5</v>
       </c>
-      <c r="W12" s="13"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+      <c r="AA12" s="12"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
@@ -1714,93 +1800,100 @@
       <c r="BF12" s="4"/>
       <c r="BG12" s="4"/>
       <c r="BH12" s="4"/>
-    </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI12" s="4"/>
+      <c r="BJ12" s="4"/>
+      <c r="BK12" s="4"/>
+      <c r="BL12" s="4"/>
+    </row>
+    <row r="13" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="12">
         <f t="shared" ref="C13:H13" si="1">+C11-C12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f t="shared" si="1"/>
         <v>1088.6999999999998</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <f t="shared" si="1"/>
         <v>931.10000000000014</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <f t="shared" si="1"/>
         <v>999.00000000000023</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <f t="shared" si="1"/>
         <v>990.60000000000014</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f>+I11-I12</f>
         <v>1105.4999999999998</v>
       </c>
-      <c r="J13" s="13">
-        <f t="shared" ref="J13:N13" si="2">+J11-J12</f>
+      <c r="J13" s="12">
+        <f t="shared" ref="J13:O13" si="2">+J11-J12</f>
         <v>1082.9000000000001</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="12">
         <f t="shared" si="2"/>
         <v>975.09999999999991</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="12">
         <f t="shared" si="2"/>
         <v>894.60000000000014</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="12">
         <f t="shared" si="2"/>
         <v>884.90000000000009</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="12">
         <f t="shared" si="2"/>
         <v>525.10000000000036</v>
       </c>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13">
-        <f t="shared" ref="P13:T13" si="3">+P11-P12</f>
+      <c r="O13" s="12">
+        <f t="shared" si="2"/>
+        <v>888.9</v>
+      </c>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12">
+        <f t="shared" ref="T13:X13" si="3">+T11-T12</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="U13" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R13" s="13">
+      <c r="V13" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S13" s="13">
+      <c r="W13" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T13" s="13">
+      <c r="X13" s="12">
         <f t="shared" si="3"/>
         <v>3986.6000000000004</v>
       </c>
-      <c r="U13" s="13">
-        <f>+U11-U12</f>
+      <c r="Y13" s="12">
+        <f>+Y11-Y12</f>
         <v>4178.0000000000009</v>
       </c>
-      <c r="V13" s="13">
-        <f>+V11-V12</f>
+      <c r="Z13" s="12">
+        <f>+Z11-Z12</f>
         <v>3279.7</v>
       </c>
-      <c r="W13" s="13"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
+      <c r="AA13" s="12"/>
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
@@ -1834,63 +1927,69 @@
       <c r="BF13" s="4"/>
       <c r="BG13" s="4"/>
       <c r="BH13" s="4"/>
-    </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI13" s="4"/>
+      <c r="BJ13" s="4"/>
+      <c r="BK13" s="4"/>
+      <c r="BL13" s="4"/>
+    </row>
+    <row r="14" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12">
         <v>11.3</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>11.3</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>5.2</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="12">
         <v>5.9</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="12">
         <v>8.1999999999999993</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="12">
         <v>5.5</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="12">
         <v>6.9</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="12">
         <v>5.2</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="12">
         <f t="shared" si="0"/>
         <v>74.800000000000011</v>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13">
+      <c r="O14" s="12">
+        <v>23.9</v>
+      </c>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12">
         <v>38.5</v>
       </c>
-      <c r="U14" s="13">
+      <c r="Y14" s="12">
         <v>24.3</v>
       </c>
-      <c r="V14" s="13">
+      <c r="Z14" s="12">
         <v>92.4</v>
       </c>
-      <c r="W14" s="13"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="AA14" s="12"/>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
@@ -1924,66 +2023,73 @@
       <c r="BF14" s="4"/>
       <c r="BG14" s="4"/>
       <c r="BH14" s="4"/>
-    </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI14" s="4"/>
+      <c r="BJ14" s="4"/>
+      <c r="BK14" s="4"/>
+      <c r="BL14" s="4"/>
+    </row>
+    <row r="15" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12">
         <v>863.7</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>848</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>845.3</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="12">
         <v>879.3</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <v>873.4</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="12">
         <v>982.2</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="12">
         <f>904.9+18</f>
         <v>922.9</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="12">
         <v>914.7</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="12">
         <f>850.6+10.1</f>
         <v>860.7</v>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="12">
         <f t="shared" si="0"/>
         <v>1030.9999999999995</v>
       </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13">
+      <c r="O15" s="12">
+        <f>848.5+12.6</f>
+        <v>861.1</v>
+      </c>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12">
         <v>3403.5</v>
       </c>
-      <c r="U15" s="13">
+      <c r="Y15" s="12">
         <v>3580.2</v>
       </c>
-      <c r="V15" s="13">
+      <c r="Z15" s="12">
         <f>3537.7+191.6</f>
         <v>3729.2999999999997</v>
       </c>
-      <c r="W15" s="13"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="AA15" s="12"/>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
@@ -2017,93 +2123,100 @@
       <c r="BF15" s="4"/>
       <c r="BG15" s="4"/>
       <c r="BH15" s="4"/>
-    </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI15" s="4"/>
+      <c r="BJ15" s="4"/>
+      <c r="BK15" s="4"/>
+      <c r="BL15" s="4"/>
+    </row>
+    <row r="16" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="12">
         <f t="shared" ref="C16:H16" si="4">+C13+C14-C15</f>
         <v>0</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <f t="shared" si="4"/>
         <v>236.29999999999973</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <f t="shared" si="4"/>
         <v>94.400000000000091</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <f t="shared" si="4"/>
         <v>158.90000000000032</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="12">
         <f t="shared" si="4"/>
         <v>117.20000000000016</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <f>+I13+I14-I15</f>
         <v>236.99999999999989</v>
       </c>
-      <c r="J16" s="13">
-        <f t="shared" ref="J16:N16" si="5">+J13+J14-J15</f>
+      <c r="J16" s="12">
+        <f t="shared" ref="J16:O16" si="5">+J13+J14-J15</f>
         <v>108.90000000000009</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="12">
         <f t="shared" si="5"/>
         <v>57.699999999999932</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="12">
         <f t="shared" si="5"/>
         <v>-13.199999999999932</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="12">
         <f t="shared" si="5"/>
         <v>29.400000000000091</v>
       </c>
-      <c r="N16" s="13">
+      <c r="N16" s="12">
         <f t="shared" si="5"/>
         <v>-431.09999999999923</v>
       </c>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13">
-        <f t="shared" ref="P16:T16" si="6">+P13+P14-P15</f>
+      <c r="O16" s="12">
+        <f t="shared" si="5"/>
+        <v>51.699999999999932</v>
+      </c>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12">
+        <f t="shared" ref="T16:X16" si="6">+T13+T14-T15</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="U16" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R16" s="13">
+      <c r="V16" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S16" s="13">
+      <c r="W16" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T16" s="13">
+      <c r="X16" s="12">
         <f t="shared" si="6"/>
         <v>621.60000000000036</v>
       </c>
-      <c r="U16" s="13">
-        <f>+U13+U14-U15</f>
+      <c r="Y16" s="12">
+        <f>+Y13+Y14-Y15</f>
         <v>622.10000000000127</v>
       </c>
-      <c r="V16" s="13">
-        <f>+V13+V14-V15</f>
+      <c r="Z16" s="12">
+        <f>+Z13+Z14-Z15</f>
         <v>-357.19999999999982</v>
       </c>
-      <c r="W16" s="13"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="AA16" s="12"/>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
@@ -2137,64 +2250,70 @@
       <c r="BF16" s="4"/>
       <c r="BG16" s="4"/>
       <c r="BH16" s="4"/>
-    </row>
-    <row r="17" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI16" s="4"/>
+      <c r="BJ16" s="4"/>
+      <c r="BK16" s="4"/>
+      <c r="BL16" s="4"/>
+    </row>
+    <row r="17" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12">
         <v>45.5</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>67.099999999999994</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>26.8</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="12">
         <v>42.6</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <v>46.7</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="12">
         <v>43.5</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="12">
         <v>42</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="12">
         <f>84.6+46.6</f>
         <v>131.19999999999999</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="12">
         <v>43.8</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="12">
         <f t="shared" si="0"/>
         <v>-51.300000000000011</v>
       </c>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13">
+      <c r="O17" s="12">
+        <v>15.6</v>
+      </c>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12">
         <v>143.30000000000001</v>
       </c>
-      <c r="U17" s="13">
+      <c r="Y17" s="12">
         <v>159.69999999999999</v>
       </c>
-      <c r="V17" s="13">
+      <c r="Z17" s="12">
         <v>165.7</v>
       </c>
-      <c r="W17" s="13"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="AA17" s="12"/>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
@@ -2228,93 +2347,100 @@
       <c r="BF17" s="4"/>
       <c r="BG17" s="4"/>
       <c r="BH17" s="4"/>
-    </row>
-    <row r="18" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI17" s="4"/>
+      <c r="BJ17" s="4"/>
+      <c r="BK17" s="4"/>
+      <c r="BL17" s="4"/>
+    </row>
+    <row r="18" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="12">
         <f t="shared" ref="C18:D18" si="7">+C16-C17</f>
         <v>0</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <f>+E16-E17</f>
         <v>190.79999999999973</v>
       </c>
-      <c r="F18" s="13">
-        <f t="shared" ref="F18:N18" si="8">+F16-F17</f>
+      <c r="F18" s="12">
+        <f t="shared" ref="F18:O18" si="8">+F16-F17</f>
         <v>27.300000000000097</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <f t="shared" si="8"/>
         <v>132.10000000000031</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="12">
         <f t="shared" si="8"/>
         <v>74.600000000000165</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <f t="shared" si="8"/>
         <v>190.2999999999999</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="12">
         <f t="shared" si="8"/>
         <v>65.400000000000091</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="12">
         <f t="shared" si="8"/>
         <v>15.699999999999932</v>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="12">
         <f t="shared" si="8"/>
         <v>-144.39999999999992</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="12">
         <f t="shared" si="8"/>
         <v>-14.399999999999906</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="12">
         <f t="shared" si="8"/>
         <v>-379.79999999999922</v>
       </c>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13">
-        <f t="shared" ref="P18:T18" si="9">+P16-P17</f>
+      <c r="O18" s="12">
+        <f t="shared" si="8"/>
+        <v>36.09999999999993</v>
+      </c>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12">
+        <f t="shared" ref="T18:X18" si="9">+T16-T17</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="U18" s="12">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R18" s="13">
+      <c r="V18" s="12">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S18" s="13">
+      <c r="W18" s="12">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T18" s="13">
+      <c r="X18" s="12">
         <f t="shared" si="9"/>
         <v>478.30000000000035</v>
       </c>
-      <c r="U18" s="13">
-        <f>+U16-U17</f>
+      <c r="Y18" s="12">
+        <f>+Y16-Y17</f>
         <v>462.40000000000128</v>
       </c>
-      <c r="V18" s="13">
-        <f>+V16-V17</f>
+      <c r="Z18" s="12">
+        <f>+Z16-Z17</f>
         <v>-522.89999999999986</v>
       </c>
-      <c r="W18" s="13"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="AA18" s="12"/>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
@@ -2348,63 +2474,69 @@
       <c r="BF18" s="4"/>
       <c r="BG18" s="4"/>
       <c r="BH18" s="4"/>
-    </row>
-    <row r="19" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI18" s="4"/>
+      <c r="BJ18" s="4"/>
+      <c r="BK18" s="4"/>
+      <c r="BL18" s="4"/>
+    </row>
+    <row r="19" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12">
         <v>47.9</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="12">
         <v>33</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="12">
         <v>18.399999999999999</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <v>47.8</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="12">
         <v>20.7</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="12">
         <v>4.2</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="12">
         <v>94.7</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="12">
         <v>37.9</v>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="12">
         <f t="shared" si="0"/>
         <v>-16.100000000000009</v>
       </c>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13">
+      <c r="O19" s="12">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12">
         <v>117.8</v>
       </c>
-      <c r="U19" s="13">
+      <c r="Y19" s="12">
         <v>120</v>
       </c>
-      <c r="V19" s="13">
+      <c r="Z19" s="12">
         <v>120.7</v>
       </c>
-      <c r="W19" s="13"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
+      <c r="AA19" s="12"/>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
@@ -2438,93 +2570,100 @@
       <c r="BF19" s="4"/>
       <c r="BG19" s="4"/>
       <c r="BH19" s="4"/>
-    </row>
-    <row r="20" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI19" s="4"/>
+      <c r="BJ19" s="4"/>
+      <c r="BK19" s="4"/>
+      <c r="BL19" s="4"/>
+    </row>
+    <row r="20" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="12">
         <f t="shared" ref="C20:D20" si="10">+C18-C19</f>
         <v>0</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="12">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <f>+E18-E19</f>
         <v>142.89999999999972</v>
       </c>
-      <c r="F20" s="13">
-        <f t="shared" ref="F20:N20" si="11">+F18-F19</f>
+      <c r="F20" s="12">
+        <f t="shared" ref="F20:O20" si="11">+F18-F19</f>
         <v>22.400000000000098</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="12">
         <f t="shared" si="11"/>
         <v>99.100000000000307</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="12">
         <f t="shared" si="11"/>
         <v>56.200000000000166</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <f t="shared" si="11"/>
         <v>142.49999999999989</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="12">
         <f t="shared" si="11"/>
         <v>44.700000000000088</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="12">
         <f t="shared" si="11"/>
         <v>11.499999999999932</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="12">
         <f t="shared" si="11"/>
         <v>-239.09999999999991</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M20" s="12">
         <f t="shared" si="11"/>
         <v>-52.299999999999905</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="12">
         <f t="shared" si="11"/>
         <v>-363.69999999999919</v>
       </c>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13">
-        <f t="shared" ref="P20:T20" si="12">+P18-P19</f>
+      <c r="O20" s="12">
+        <f t="shared" si="11"/>
+        <v>26.29999999999993</v>
+      </c>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12">
+        <f t="shared" ref="T20:X20" si="12">+T18-T19</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="13">
+      <c r="U20" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R20" s="13">
+      <c r="V20" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S20" s="13">
+      <c r="W20" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T20" s="13">
+      <c r="X20" s="12">
         <f t="shared" si="12"/>
         <v>360.50000000000034</v>
       </c>
-      <c r="U20" s="13">
-        <f>+U18-U19</f>
+      <c r="Y20" s="12">
+        <f>+Y18-Y19</f>
         <v>342.40000000000128</v>
       </c>
-      <c r="V20" s="13">
-        <f>+V18-V19</f>
+      <c r="Z20" s="12">
+        <f>+Z18-Z19</f>
         <v>-643.59999999999991</v>
       </c>
-      <c r="W20" s="13"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="4"/>
+      <c r="AA20" s="12"/>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
@@ -2558,64 +2697,70 @@
       <c r="BF20" s="4"/>
       <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
-    </row>
-    <row r="21" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI20" s="4"/>
+      <c r="BJ20" s="4"/>
+      <c r="BK20" s="4"/>
+      <c r="BL20" s="4"/>
+    </row>
+    <row r="21" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13">
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12">
         <v>11.3</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="12">
         <v>21.6</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="12">
         <v>11.8</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="12">
         <v>14.3</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <v>14.6</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="12">
         <v>20.100000000000001</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="12">
         <v>11.1</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="12">
         <v>7.9</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="12">
         <v>10</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="12">
         <f t="shared" si="0"/>
         <v>-27.099999999999998</v>
       </c>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="13">
+      <c r="O21" s="12">
+        <v>0</v>
+      </c>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12">
         <v>55.7</v>
       </c>
-      <c r="U21" s="13">
+      <c r="Y21" s="12">
         <v>60.7</v>
       </c>
-      <c r="V21" s="13">
+      <c r="Z21" s="12">
         <f>30.3-28.4</f>
         <v>1.9000000000000021</v>
       </c>
-      <c r="W21" s="13"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="4"/>
+      <c r="AA21" s="12"/>
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
@@ -2649,93 +2794,100 @@
       <c r="BF21" s="4"/>
       <c r="BG21" s="4"/>
       <c r="BH21" s="4"/>
-    </row>
-    <row r="22" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI21" s="4"/>
+      <c r="BJ21" s="4"/>
+      <c r="BK21" s="4"/>
+      <c r="BL21" s="4"/>
+    </row>
+    <row r="22" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="12">
         <f t="shared" ref="C22:D22" si="13">+C20-C21</f>
         <v>0</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="12">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="12">
         <f>+E20-E21</f>
         <v>131.59999999999971</v>
       </c>
-      <c r="F22" s="13">
-        <f t="shared" ref="F22:N22" si="14">+F20-F21</f>
+      <c r="F22" s="12">
+        <f t="shared" ref="F22:O22" si="14">+F20-F21</f>
         <v>0.80000000000009663</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="12">
         <f t="shared" si="14"/>
         <v>87.30000000000031</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="12">
         <f t="shared" si="14"/>
         <v>41.900000000000162</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <f t="shared" si="14"/>
         <v>127.89999999999989</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="12">
         <f t="shared" si="14"/>
         <v>24.600000000000087</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="12">
         <f t="shared" si="14"/>
         <v>0.39999999999993285</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="12">
         <f t="shared" si="14"/>
         <v>-246.99999999999991</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="12">
         <f t="shared" si="14"/>
         <v>-62.299999999999905</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="12">
         <f t="shared" si="14"/>
         <v>-336.59999999999917</v>
       </c>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13">
-        <f t="shared" ref="P22:T22" si="15">+P20-P21</f>
+      <c r="O22" s="12">
+        <f t="shared" si="14"/>
+        <v>26.29999999999993</v>
+      </c>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12">
+        <f t="shared" ref="T22:X22" si="15">+T20-T21</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="13">
+      <c r="U22" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="R22" s="13">
+      <c r="V22" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="S22" s="13">
+      <c r="W22" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="T22" s="13">
+      <c r="X22" s="12">
         <f t="shared" si="15"/>
         <v>304.80000000000035</v>
       </c>
-      <c r="U22" s="13">
-        <f>+U20-U21</f>
+      <c r="Y22" s="12">
+        <f>+Y20-Y21</f>
         <v>281.7000000000013</v>
       </c>
-      <c r="V22" s="13">
-        <f>+V20-V21</f>
+      <c r="Z22" s="12">
+        <f>+Z20-Z21</f>
         <v>-645.49999999999989</v>
       </c>
-      <c r="W22" s="13"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="4"/>
+      <c r="AA22" s="12"/>
       <c r="AB22" s="4"/>
       <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
@@ -2769,8 +2921,12 @@
       <c r="BF22" s="4"/>
       <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>
-    </row>
-    <row r="23" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI22" s="4"/>
+      <c r="BJ22" s="4"/>
+      <c r="BK22" s="4"/>
+      <c r="BL22" s="4"/>
+    </row>
+    <row r="23" spans="2:64" x14ac:dyDescent="0.2">
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -2829,8 +2985,12 @@
       <c r="BF23" s="4"/>
       <c r="BG23" s="4"/>
       <c r="BH23" s="4"/>
-    </row>
-    <row r="24" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI23" s="4"/>
+      <c r="BJ23" s="4"/>
+      <c r="BK23" s="4"/>
+      <c r="BL23" s="4"/>
+    </row>
+    <row r="24" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>30</v>
       </c>
@@ -2847,7 +3007,7 @@
         <v>0.87838739821118483</v>
       </c>
       <c r="F24" s="7">
-        <f t="shared" ref="F24:N24" si="17">+F22/F25</f>
+        <f t="shared" ref="F24:O24" si="17">+F22/F25</f>
         <v>5.3386720053393167E-3</v>
       </c>
       <c r="G24" s="7">
@@ -2882,39 +3042,42 @@
         <f t="shared" si="17"/>
         <v>-2.2824981352139364</v>
       </c>
-      <c r="O24" s="4"/>
-      <c r="P24" s="7" t="e">
-        <f t="shared" ref="P24:S24" si="18">+P22/P25</f>
+      <c r="O24" s="7">
+        <f t="shared" si="17"/>
+        <v>0.17863207226787972</v>
+      </c>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="7" t="e">
+        <f t="shared" ref="T24:W24" si="18">+T22/T25</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q24" s="7" t="e">
+      <c r="U24" s="7" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R24" s="7" t="e">
+      <c r="V24" s="7" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S24" s="7" t="e">
+      <c r="W24" s="7" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T24" s="7">
-        <f>+T22/T25</f>
+      <c r="X24" s="7">
+        <f>+X22/X25</f>
         <v>2.0340340340340366</v>
       </c>
-      <c r="U24" s="7">
-        <f t="shared" ref="U24:V24" si="19">+U22/U25</f>
+      <c r="Y24" s="7">
+        <f t="shared" ref="Y24:Z24" si="19">+Y22/Y25</f>
         <v>1.886552370747397</v>
       </c>
-      <c r="V24" s="7">
+      <c r="Z24" s="7">
         <f t="shared" si="19"/>
         <v>-4.3789430839156092</v>
       </c>
-      <c r="W24" s="4"/>
-      <c r="X24" s="4"/>
-      <c r="Y24" s="4"/>
-      <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
       <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
@@ -2949,8 +3112,12 @@
       <c r="BF24" s="4"/>
       <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
-    </row>
-    <row r="25" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI24" s="4"/>
+      <c r="BJ24" s="4"/>
+      <c r="BK24" s="4"/>
+      <c r="BL24" s="4"/>
+    </row>
+    <row r="25" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>3</v>
       </c>
@@ -2986,24 +3153,26 @@
       <c r="N25" s="4">
         <v>147.47</v>
       </c>
-      <c r="O25" s="4"/>
+      <c r="O25" s="4">
+        <v>147.22999999999999</v>
+      </c>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
-      <c r="T25" s="4">
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4">
         <v>149.85</v>
       </c>
-      <c r="U25" s="4">
+      <c r="Y25" s="4">
         <v>149.32</v>
       </c>
-      <c r="V25" s="4">
+      <c r="Z25" s="4">
         <v>147.41</v>
       </c>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
-      <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
@@ -3038,8 +3207,12 @@
       <c r="BF25" s="4"/>
       <c r="BG25" s="4"/>
       <c r="BH25" s="4"/>
-    </row>
-    <row r="26" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI25" s="4"/>
+      <c r="BJ25" s="4"/>
+      <c r="BK25" s="4"/>
+      <c r="BL25" s="4"/>
+    </row>
+    <row r="26" spans="2:64" x14ac:dyDescent="0.2">
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -3098,8 +3271,12 @@
       <c r="BF26" s="4"/>
       <c r="BG26" s="4"/>
       <c r="BH26" s="4"/>
-    </row>
-    <row r="27" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI26" s="4"/>
+      <c r="BJ26" s="4"/>
+      <c r="BK26" s="4"/>
+      <c r="BL26" s="4"/>
+    </row>
+    <row r="27" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B27" s="5" t="s">
         <v>31</v>
       </c>
@@ -3118,7 +3295,7 @@
         <v>0.15497931591161329</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" ref="K27:N27" si="20">+K11/G11-1</f>
+        <f t="shared" ref="K27:O27" si="20">+K11/G11-1</f>
         <v>-1.2510107976977713E-2</v>
       </c>
       <c r="L27" s="8">
@@ -3133,10 +3310,13 @@
         <f t="shared" si="20"/>
         <v>-0.42242508954311164</v>
       </c>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
+      <c r="O27" s="8">
+        <f t="shared" si="20"/>
+        <v>-0.10221579961464355</v>
+      </c>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
       <c r="S27" s="6"/>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
@@ -3144,10 +3324,10 @@
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
       <c r="Y27" s="6"/>
-      <c r="Z27" s="4"/>
-      <c r="AA27" s="4"/>
-      <c r="AB27" s="4"/>
-      <c r="AC27" s="4"/>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="6"/>
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
@@ -3179,8 +3359,12 @@
       <c r="BF27" s="4"/>
       <c r="BG27" s="4"/>
       <c r="BH27" s="4"/>
-    </row>
-    <row r="28" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI27" s="4"/>
+      <c r="BJ27" s="4"/>
+      <c r="BK27" s="4"/>
+      <c r="BL27" s="4"/>
+    </row>
+    <row r="28" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>32</v>
       </c>
@@ -3229,13 +3413,16 @@
         <v>0.45247226057166234</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" ref="N28" si="24">+N13/N11</f>
+        <f t="shared" ref="N28:O28" si="24">+N13/N11</f>
         <v>0.39711109430537722</v>
       </c>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
+      <c r="O28" s="9">
+        <f t="shared" si="24"/>
+        <v>0.47692885502736343</v>
+      </c>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
@@ -3278,8 +3465,12 @@
       <c r="BF28" s="4"/>
       <c r="BG28" s="4"/>
       <c r="BH28" s="4"/>
-    </row>
-    <row r="29" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI28" s="4"/>
+      <c r="BJ28" s="4"/>
+      <c r="BK28" s="4"/>
+      <c r="BL28" s="4"/>
+    </row>
+    <row r="29" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>33</v>
       </c>
@@ -3328,13 +3519,16 @@
         <v>1.5032980518484475E-2</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" ref="N29" si="28">+N16/N11</f>
+        <f t="shared" ref="N29:O29" si="28">+N16/N11</f>
         <v>-0.32602283899266365</v>
       </c>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
+      <c r="O29" s="9">
+        <f t="shared" si="28"/>
+        <v>2.7739027792681583E-2</v>
+      </c>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
@@ -3377,8 +3571,12 @@
       <c r="BF29" s="4"/>
       <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
-    </row>
-    <row r="30" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI29" s="4"/>
+      <c r="BJ29" s="4"/>
+      <c r="BK29" s="4"/>
+      <c r="BL29" s="4"/>
+    </row>
+    <row r="30" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>34</v>
       </c>
@@ -3427,13 +3625,16 @@
         <v>-2.6319444444444615</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" ref="N30" si="32">+N19/N18</f>
+        <f t="shared" ref="N30:O30" si="32">+N19/N18</f>
         <v>4.239073196419179E-2</v>
       </c>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
+      <c r="O30" s="9">
+        <f t="shared" si="32"/>
+        <v>0.27146814404432185</v>
+      </c>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
@@ -3476,8 +3677,12 @@
       <c r="BF30" s="4"/>
       <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
-    </row>
-    <row r="31" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI30" s="4"/>
+      <c r="BJ30" s="4"/>
+      <c r="BK30" s="4"/>
+      <c r="BL30" s="4"/>
+    </row>
+    <row r="31" spans="2:64" x14ac:dyDescent="0.2">
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -3536,8 +3741,12 @@
       <c r="BF31" s="4"/>
       <c r="BG31" s="4"/>
       <c r="BH31" s="4"/>
-    </row>
-    <row r="32" spans="2:60" x14ac:dyDescent="0.2">
+      <c r="BI31" s="4"/>
+      <c r="BJ31" s="4"/>
+      <c r="BK31" s="4"/>
+      <c r="BL31" s="4"/>
+    </row>
+    <row r="32" spans="2:64" x14ac:dyDescent="0.2">
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -3596,8 +3805,12 @@
       <c r="BF32" s="4"/>
       <c r="BG32" s="4"/>
       <c r="BH32" s="4"/>
-    </row>
-    <row r="33" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI32" s="4"/>
+      <c r="BJ32" s="4"/>
+      <c r="BK32" s="4"/>
+      <c r="BL32" s="4"/>
+    </row>
+    <row r="33" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -3656,8 +3869,12 @@
       <c r="BF33" s="4"/>
       <c r="BG33" s="4"/>
       <c r="BH33" s="4"/>
-    </row>
-    <row r="34" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI33" s="4"/>
+      <c r="BJ33" s="4"/>
+      <c r="BK33" s="4"/>
+      <c r="BL33" s="4"/>
+    </row>
+    <row r="34" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -3716,8 +3933,12 @@
       <c r="BF34" s="4"/>
       <c r="BG34" s="4"/>
       <c r="BH34" s="4"/>
-    </row>
-    <row r="35" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI34" s="4"/>
+      <c r="BJ34" s="4"/>
+      <c r="BK34" s="4"/>
+      <c r="BL34" s="4"/>
+    </row>
+    <row r="35" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -3776,8 +3997,12 @@
       <c r="BF35" s="4"/>
       <c r="BG35" s="4"/>
       <c r="BH35" s="4"/>
-    </row>
-    <row r="36" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI35" s="4"/>
+      <c r="BJ35" s="4"/>
+      <c r="BK35" s="4"/>
+      <c r="BL35" s="4"/>
+    </row>
+    <row r="36" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -3836,8 +4061,12 @@
       <c r="BF36" s="4"/>
       <c r="BG36" s="4"/>
       <c r="BH36" s="4"/>
-    </row>
-    <row r="37" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI36" s="4"/>
+      <c r="BJ36" s="4"/>
+      <c r="BK36" s="4"/>
+      <c r="BL36" s="4"/>
+    </row>
+    <row r="37" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -3896,8 +4125,12 @@
       <c r="BF37" s="4"/>
       <c r="BG37" s="4"/>
       <c r="BH37" s="4"/>
-    </row>
-    <row r="38" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI37" s="4"/>
+      <c r="BJ37" s="4"/>
+      <c r="BK37" s="4"/>
+      <c r="BL37" s="4"/>
+    </row>
+    <row r="38" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -3956,8 +4189,12 @@
       <c r="BF38" s="4"/>
       <c r="BG38" s="4"/>
       <c r="BH38" s="4"/>
-    </row>
-    <row r="39" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI38" s="4"/>
+      <c r="BJ38" s="4"/>
+      <c r="BK38" s="4"/>
+      <c r="BL38" s="4"/>
+    </row>
+    <row r="39" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -4016,8 +4253,12 @@
       <c r="BF39" s="4"/>
       <c r="BG39" s="4"/>
       <c r="BH39" s="4"/>
-    </row>
-    <row r="40" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI39" s="4"/>
+      <c r="BJ39" s="4"/>
+      <c r="BK39" s="4"/>
+      <c r="BL39" s="4"/>
+    </row>
+    <row r="40" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -4076,8 +4317,12 @@
       <c r="BF40" s="4"/>
       <c r="BG40" s="4"/>
       <c r="BH40" s="4"/>
-    </row>
-    <row r="41" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI40" s="4"/>
+      <c r="BJ40" s="4"/>
+      <c r="BK40" s="4"/>
+      <c r="BL40" s="4"/>
+    </row>
+    <row r="41" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -4136,8 +4381,12 @@
       <c r="BF41" s="4"/>
       <c r="BG41" s="4"/>
       <c r="BH41" s="4"/>
-    </row>
-    <row r="42" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI41" s="4"/>
+      <c r="BJ41" s="4"/>
+      <c r="BK41" s="4"/>
+      <c r="BL41" s="4"/>
+    </row>
+    <row r="42" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -4196,8 +4445,12 @@
       <c r="BF42" s="4"/>
       <c r="BG42" s="4"/>
       <c r="BH42" s="4"/>
-    </row>
-    <row r="43" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+    </row>
+    <row r="43" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -4256,8 +4509,12 @@
       <c r="BF43" s="4"/>
       <c r="BG43" s="4"/>
       <c r="BH43" s="4"/>
-    </row>
-    <row r="44" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI43" s="4"/>
+      <c r="BJ43" s="4"/>
+      <c r="BK43" s="4"/>
+      <c r="BL43" s="4"/>
+    </row>
+    <row r="44" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -4316,8 +4573,12 @@
       <c r="BF44" s="4"/>
       <c r="BG44" s="4"/>
       <c r="BH44" s="4"/>
-    </row>
-    <row r="45" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI44" s="4"/>
+      <c r="BJ44" s="4"/>
+      <c r="BK44" s="4"/>
+      <c r="BL44" s="4"/>
+    </row>
+    <row r="45" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -4376,8 +4637,12 @@
       <c r="BF45" s="4"/>
       <c r="BG45" s="4"/>
       <c r="BH45" s="4"/>
-    </row>
-    <row r="46" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI45" s="4"/>
+      <c r="BJ45" s="4"/>
+      <c r="BK45" s="4"/>
+      <c r="BL45" s="4"/>
+    </row>
+    <row r="46" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -4436,8 +4701,12 @@
       <c r="BF46" s="4"/>
       <c r="BG46" s="4"/>
       <c r="BH46" s="4"/>
-    </row>
-    <row r="47" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI46" s="4"/>
+      <c r="BJ46" s="4"/>
+      <c r="BK46" s="4"/>
+      <c r="BL46" s="4"/>
+    </row>
+    <row r="47" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -4496,8 +4765,12 @@
       <c r="BF47" s="4"/>
       <c r="BG47" s="4"/>
       <c r="BH47" s="4"/>
-    </row>
-    <row r="48" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI47" s="4"/>
+      <c r="BJ47" s="4"/>
+      <c r="BK47" s="4"/>
+      <c r="BL47" s="4"/>
+    </row>
+    <row r="48" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -4556,8 +4829,12 @@
       <c r="BF48" s="4"/>
       <c r="BG48" s="4"/>
       <c r="BH48" s="4"/>
-    </row>
-    <row r="49" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI48" s="4"/>
+      <c r="BJ48" s="4"/>
+      <c r="BK48" s="4"/>
+      <c r="BL48" s="4"/>
+    </row>
+    <row r="49" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -4616,8 +4893,12 @@
       <c r="BF49" s="4"/>
       <c r="BG49" s="4"/>
       <c r="BH49" s="4"/>
-    </row>
-    <row r="50" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI49" s="4"/>
+      <c r="BJ49" s="4"/>
+      <c r="BK49" s="4"/>
+      <c r="BL49" s="4"/>
+    </row>
+    <row r="50" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -4676,8 +4957,12 @@
       <c r="BF50" s="4"/>
       <c r="BG50" s="4"/>
       <c r="BH50" s="4"/>
-    </row>
-    <row r="51" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI50" s="4"/>
+      <c r="BJ50" s="4"/>
+      <c r="BK50" s="4"/>
+      <c r="BL50" s="4"/>
+    </row>
+    <row r="51" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -4736,8 +5021,12 @@
       <c r="BF51" s="4"/>
       <c r="BG51" s="4"/>
       <c r="BH51" s="4"/>
-    </row>
-    <row r="52" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI51" s="4"/>
+      <c r="BJ51" s="4"/>
+      <c r="BK51" s="4"/>
+      <c r="BL51" s="4"/>
+    </row>
+    <row r="52" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -4796,8 +5085,12 @@
       <c r="BF52" s="4"/>
       <c r="BG52" s="4"/>
       <c r="BH52" s="4"/>
-    </row>
-    <row r="53" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI52" s="4"/>
+      <c r="BJ52" s="4"/>
+      <c r="BK52" s="4"/>
+      <c r="BL52" s="4"/>
+    </row>
+    <row r="53" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -4856,8 +5149,12 @@
       <c r="BF53" s="4"/>
       <c r="BG53" s="4"/>
       <c r="BH53" s="4"/>
-    </row>
-    <row r="54" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI53" s="4"/>
+      <c r="BJ53" s="4"/>
+      <c r="BK53" s="4"/>
+      <c r="BL53" s="4"/>
+    </row>
+    <row r="54" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -4916,8 +5213,12 @@
       <c r="BF54" s="4"/>
       <c r="BG54" s="4"/>
       <c r="BH54" s="4"/>
-    </row>
-    <row r="55" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI54" s="4"/>
+      <c r="BJ54" s="4"/>
+      <c r="BK54" s="4"/>
+      <c r="BL54" s="4"/>
+    </row>
+    <row r="55" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -4976,8 +5277,12 @@
       <c r="BF55" s="4"/>
       <c r="BG55" s="4"/>
       <c r="BH55" s="4"/>
-    </row>
-    <row r="56" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI55" s="4"/>
+      <c r="BJ55" s="4"/>
+      <c r="BK55" s="4"/>
+      <c r="BL55" s="4"/>
+    </row>
+    <row r="56" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -5036,8 +5341,12 @@
       <c r="BF56" s="4"/>
       <c r="BG56" s="4"/>
       <c r="BH56" s="4"/>
-    </row>
-    <row r="57" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI56" s="4"/>
+      <c r="BJ56" s="4"/>
+      <c r="BK56" s="4"/>
+      <c r="BL56" s="4"/>
+    </row>
+    <row r="57" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -5096,8 +5405,12 @@
       <c r="BF57" s="4"/>
       <c r="BG57" s="4"/>
       <c r="BH57" s="4"/>
-    </row>
-    <row r="58" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI57" s="4"/>
+      <c r="BJ57" s="4"/>
+      <c r="BK57" s="4"/>
+      <c r="BL57" s="4"/>
+    </row>
+    <row r="58" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -5156,8 +5469,12 @@
       <c r="BF58" s="4"/>
       <c r="BG58" s="4"/>
       <c r="BH58" s="4"/>
-    </row>
-    <row r="59" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI58" s="4"/>
+      <c r="BJ58" s="4"/>
+      <c r="BK58" s="4"/>
+      <c r="BL58" s="4"/>
+    </row>
+    <row r="59" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -5216,8 +5533,12 @@
       <c r="BF59" s="4"/>
       <c r="BG59" s="4"/>
       <c r="BH59" s="4"/>
-    </row>
-    <row r="60" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI59" s="4"/>
+      <c r="BJ59" s="4"/>
+      <c r="BK59" s="4"/>
+      <c r="BL59" s="4"/>
+    </row>
+    <row r="60" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -5276,8 +5597,12 @@
       <c r="BF60" s="4"/>
       <c r="BG60" s="4"/>
       <c r="BH60" s="4"/>
-    </row>
-    <row r="61" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI60" s="4"/>
+      <c r="BJ60" s="4"/>
+      <c r="BK60" s="4"/>
+      <c r="BL60" s="4"/>
+    </row>
+    <row r="61" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -5336,8 +5661,12 @@
       <c r="BF61" s="4"/>
       <c r="BG61" s="4"/>
       <c r="BH61" s="4"/>
-    </row>
-    <row r="62" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI61" s="4"/>
+      <c r="BJ61" s="4"/>
+      <c r="BK61" s="4"/>
+      <c r="BL61" s="4"/>
+    </row>
+    <row r="62" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -5396,8 +5725,12 @@
       <c r="BF62" s="4"/>
       <c r="BG62" s="4"/>
       <c r="BH62" s="4"/>
-    </row>
-    <row r="63" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI62" s="4"/>
+      <c r="BJ62" s="4"/>
+      <c r="BK62" s="4"/>
+      <c r="BL62" s="4"/>
+    </row>
+    <row r="63" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -5456,8 +5789,12 @@
       <c r="BF63" s="4"/>
       <c r="BG63" s="4"/>
       <c r="BH63" s="4"/>
-    </row>
-    <row r="64" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI63" s="4"/>
+      <c r="BJ63" s="4"/>
+      <c r="BK63" s="4"/>
+      <c r="BL63" s="4"/>
+    </row>
+    <row r="64" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -5516,8 +5853,12 @@
       <c r="BF64" s="4"/>
       <c r="BG64" s="4"/>
       <c r="BH64" s="4"/>
-    </row>
-    <row r="65" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI64" s="4"/>
+      <c r="BJ64" s="4"/>
+      <c r="BK64" s="4"/>
+      <c r="BL64" s="4"/>
+    </row>
+    <row r="65" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -5576,8 +5917,12 @@
       <c r="BF65" s="4"/>
       <c r="BG65" s="4"/>
       <c r="BH65" s="4"/>
-    </row>
-    <row r="66" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI65" s="4"/>
+      <c r="BJ65" s="4"/>
+      <c r="BK65" s="4"/>
+      <c r="BL65" s="4"/>
+    </row>
+    <row r="66" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -5636,8 +5981,12 @@
       <c r="BF66" s="4"/>
       <c r="BG66" s="4"/>
       <c r="BH66" s="4"/>
-    </row>
-    <row r="67" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI66" s="4"/>
+      <c r="BJ66" s="4"/>
+      <c r="BK66" s="4"/>
+      <c r="BL66" s="4"/>
+    </row>
+    <row r="67" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -5696,8 +6045,12 @@
       <c r="BF67" s="4"/>
       <c r="BG67" s="4"/>
       <c r="BH67" s="4"/>
-    </row>
-    <row r="68" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI67" s="4"/>
+      <c r="BJ67" s="4"/>
+      <c r="BK67" s="4"/>
+      <c r="BL67" s="4"/>
+    </row>
+    <row r="68" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -5756,8 +6109,12 @@
       <c r="BF68" s="4"/>
       <c r="BG68" s="4"/>
       <c r="BH68" s="4"/>
-    </row>
-    <row r="69" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI68" s="4"/>
+      <c r="BJ68" s="4"/>
+      <c r="BK68" s="4"/>
+      <c r="BL68" s="4"/>
+    </row>
+    <row r="69" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -5816,8 +6173,12 @@
       <c r="BF69" s="4"/>
       <c r="BG69" s="4"/>
       <c r="BH69" s="4"/>
-    </row>
-    <row r="70" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI69" s="4"/>
+      <c r="BJ69" s="4"/>
+      <c r="BK69" s="4"/>
+      <c r="BL69" s="4"/>
+    </row>
+    <row r="70" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -5876,8 +6237,12 @@
       <c r="BF70" s="4"/>
       <c r="BG70" s="4"/>
       <c r="BH70" s="4"/>
-    </row>
-    <row r="71" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI70" s="4"/>
+      <c r="BJ70" s="4"/>
+      <c r="BK70" s="4"/>
+      <c r="BL70" s="4"/>
+    </row>
+    <row r="71" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -5936,8 +6301,12 @@
       <c r="BF71" s="4"/>
       <c r="BG71" s="4"/>
       <c r="BH71" s="4"/>
-    </row>
-    <row r="72" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI71" s="4"/>
+      <c r="BJ71" s="4"/>
+      <c r="BK71" s="4"/>
+      <c r="BL71" s="4"/>
+    </row>
+    <row r="72" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -5996,8 +6365,12 @@
       <c r="BF72" s="4"/>
       <c r="BG72" s="4"/>
       <c r="BH72" s="4"/>
-    </row>
-    <row r="73" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI72" s="4"/>
+      <c r="BJ72" s="4"/>
+      <c r="BK72" s="4"/>
+      <c r="BL72" s="4"/>
+    </row>
+    <row r="73" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -6056,8 +6429,12 @@
       <c r="BF73" s="4"/>
       <c r="BG73" s="4"/>
       <c r="BH73" s="4"/>
-    </row>
-    <row r="74" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI73" s="4"/>
+      <c r="BJ73" s="4"/>
+      <c r="BK73" s="4"/>
+      <c r="BL73" s="4"/>
+    </row>
+    <row r="74" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -6116,8 +6493,12 @@
       <c r="BF74" s="4"/>
       <c r="BG74" s="4"/>
       <c r="BH74" s="4"/>
-    </row>
-    <row r="75" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI74" s="4"/>
+      <c r="BJ74" s="4"/>
+      <c r="BK74" s="4"/>
+      <c r="BL74" s="4"/>
+    </row>
+    <row r="75" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -6176,8 +6557,12 @@
       <c r="BF75" s="4"/>
       <c r="BG75" s="4"/>
       <c r="BH75" s="4"/>
-    </row>
-    <row r="76" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI75" s="4"/>
+      <c r="BJ75" s="4"/>
+      <c r="BK75" s="4"/>
+      <c r="BL75" s="4"/>
+    </row>
+    <row r="76" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -6236,8 +6621,12 @@
       <c r="BF76" s="4"/>
       <c r="BG76" s="4"/>
       <c r="BH76" s="4"/>
-    </row>
-    <row r="77" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI76" s="4"/>
+      <c r="BJ76" s="4"/>
+      <c r="BK76" s="4"/>
+      <c r="BL76" s="4"/>
+    </row>
+    <row r="77" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -6296,8 +6685,12 @@
       <c r="BF77" s="4"/>
       <c r="BG77" s="4"/>
       <c r="BH77" s="4"/>
-    </row>
-    <row r="78" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI77" s="4"/>
+      <c r="BJ77" s="4"/>
+      <c r="BK77" s="4"/>
+      <c r="BL77" s="4"/>
+    </row>
+    <row r="78" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -6356,8 +6749,12 @@
       <c r="BF78" s="4"/>
       <c r="BG78" s="4"/>
       <c r="BH78" s="4"/>
-    </row>
-    <row r="79" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI78" s="4"/>
+      <c r="BJ78" s="4"/>
+      <c r="BK78" s="4"/>
+      <c r="BL78" s="4"/>
+    </row>
+    <row r="79" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -6416,8 +6813,12 @@
       <c r="BF79" s="4"/>
       <c r="BG79" s="4"/>
       <c r="BH79" s="4"/>
-    </row>
-    <row r="80" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI79" s="4"/>
+      <c r="BJ79" s="4"/>
+      <c r="BK79" s="4"/>
+      <c r="BL79" s="4"/>
+    </row>
+    <row r="80" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -6476,8 +6877,12 @@
       <c r="BF80" s="4"/>
       <c r="BG80" s="4"/>
       <c r="BH80" s="4"/>
-    </row>
-    <row r="81" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI80" s="4"/>
+      <c r="BJ80" s="4"/>
+      <c r="BK80" s="4"/>
+      <c r="BL80" s="4"/>
+    </row>
+    <row r="81" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -6536,8 +6941,12 @@
       <c r="BF81" s="4"/>
       <c r="BG81" s="4"/>
       <c r="BH81" s="4"/>
-    </row>
-    <row r="82" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI81" s="4"/>
+      <c r="BJ81" s="4"/>
+      <c r="BK81" s="4"/>
+      <c r="BL81" s="4"/>
+    </row>
+    <row r="82" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -6596,8 +7005,12 @@
       <c r="BF82" s="4"/>
       <c r="BG82" s="4"/>
       <c r="BH82" s="4"/>
-    </row>
-    <row r="83" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI82" s="4"/>
+      <c r="BJ82" s="4"/>
+      <c r="BK82" s="4"/>
+      <c r="BL82" s="4"/>
+    </row>
+    <row r="83" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -6656,8 +7069,12 @@
       <c r="BF83" s="4"/>
       <c r="BG83" s="4"/>
       <c r="BH83" s="4"/>
-    </row>
-    <row r="84" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI83" s="4"/>
+      <c r="BJ83" s="4"/>
+      <c r="BK83" s="4"/>
+      <c r="BL83" s="4"/>
+    </row>
+    <row r="84" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -6716,8 +7133,12 @@
       <c r="BF84" s="4"/>
       <c r="BG84" s="4"/>
       <c r="BH84" s="4"/>
-    </row>
-    <row r="85" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI84" s="4"/>
+      <c r="BJ84" s="4"/>
+      <c r="BK84" s="4"/>
+      <c r="BL84" s="4"/>
+    </row>
+    <row r="85" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -6776,8 +7197,12 @@
       <c r="BF85" s="4"/>
       <c r="BG85" s="4"/>
       <c r="BH85" s="4"/>
-    </row>
-    <row r="86" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI85" s="4"/>
+      <c r="BJ85" s="4"/>
+      <c r="BK85" s="4"/>
+      <c r="BL85" s="4"/>
+    </row>
+    <row r="86" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -6836,8 +7261,12 @@
       <c r="BF86" s="4"/>
       <c r="BG86" s="4"/>
       <c r="BH86" s="4"/>
-    </row>
-    <row r="87" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI86" s="4"/>
+      <c r="BJ86" s="4"/>
+      <c r="BK86" s="4"/>
+      <c r="BL86" s="4"/>
+    </row>
+    <row r="87" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
@@ -6896,8 +7325,12 @@
       <c r="BF87" s="4"/>
       <c r="BG87" s="4"/>
       <c r="BH87" s="4"/>
-    </row>
-    <row r="88" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI87" s="4"/>
+      <c r="BJ87" s="4"/>
+      <c r="BK87" s="4"/>
+      <c r="BL87" s="4"/>
+    </row>
+    <row r="88" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -6956,8 +7389,12 @@
       <c r="BF88" s="4"/>
       <c r="BG88" s="4"/>
       <c r="BH88" s="4"/>
-    </row>
-    <row r="89" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI88" s="4"/>
+      <c r="BJ88" s="4"/>
+      <c r="BK88" s="4"/>
+      <c r="BL88" s="4"/>
+    </row>
+    <row r="89" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -7016,8 +7453,12 @@
       <c r="BF89" s="4"/>
       <c r="BG89" s="4"/>
       <c r="BH89" s="4"/>
-    </row>
-    <row r="90" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI89" s="4"/>
+      <c r="BJ89" s="4"/>
+      <c r="BK89" s="4"/>
+      <c r="BL89" s="4"/>
+    </row>
+    <row r="90" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -7076,8 +7517,12 @@
       <c r="BF90" s="4"/>
       <c r="BG90" s="4"/>
       <c r="BH90" s="4"/>
-    </row>
-    <row r="91" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI90" s="4"/>
+      <c r="BJ90" s="4"/>
+      <c r="BK90" s="4"/>
+      <c r="BL90" s="4"/>
+    </row>
+    <row r="91" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -7136,8 +7581,12 @@
       <c r="BF91" s="4"/>
       <c r="BG91" s="4"/>
       <c r="BH91" s="4"/>
-    </row>
-    <row r="92" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI91" s="4"/>
+      <c r="BJ91" s="4"/>
+      <c r="BK91" s="4"/>
+      <c r="BL91" s="4"/>
+    </row>
+    <row r="92" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -7196,8 +7645,12 @@
       <c r="BF92" s="4"/>
       <c r="BG92" s="4"/>
       <c r="BH92" s="4"/>
-    </row>
-    <row r="93" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI92" s="4"/>
+      <c r="BJ92" s="4"/>
+      <c r="BK92" s="4"/>
+      <c r="BL92" s="4"/>
+    </row>
+    <row r="93" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -7256,8 +7709,12 @@
       <c r="BF93" s="4"/>
       <c r="BG93" s="4"/>
       <c r="BH93" s="4"/>
-    </row>
-    <row r="94" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI93" s="4"/>
+      <c r="BJ93" s="4"/>
+      <c r="BK93" s="4"/>
+      <c r="BL93" s="4"/>
+    </row>
+    <row r="94" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -7316,8 +7773,12 @@
       <c r="BF94" s="4"/>
       <c r="BG94" s="4"/>
       <c r="BH94" s="4"/>
-    </row>
-    <row r="95" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI94" s="4"/>
+      <c r="BJ94" s="4"/>
+      <c r="BK94" s="4"/>
+      <c r="BL94" s="4"/>
+    </row>
+    <row r="95" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -7376,8 +7837,12 @@
       <c r="BF95" s="4"/>
       <c r="BG95" s="4"/>
       <c r="BH95" s="4"/>
-    </row>
-    <row r="96" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI95" s="4"/>
+      <c r="BJ95" s="4"/>
+      <c r="BK95" s="4"/>
+      <c r="BL95" s="4"/>
+    </row>
+    <row r="96" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -7436,8 +7901,12 @@
       <c r="BF96" s="4"/>
       <c r="BG96" s="4"/>
       <c r="BH96" s="4"/>
-    </row>
-    <row r="97" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI96" s="4"/>
+      <c r="BJ96" s="4"/>
+      <c r="BK96" s="4"/>
+      <c r="BL96" s="4"/>
+    </row>
+    <row r="97" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -7496,8 +7965,12 @@
       <c r="BF97" s="4"/>
       <c r="BG97" s="4"/>
       <c r="BH97" s="4"/>
-    </row>
-    <row r="98" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI97" s="4"/>
+      <c r="BJ97" s="4"/>
+      <c r="BK97" s="4"/>
+      <c r="BL97" s="4"/>
+    </row>
+    <row r="98" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -7556,8 +8029,12 @@
       <c r="BF98" s="4"/>
       <c r="BG98" s="4"/>
       <c r="BH98" s="4"/>
-    </row>
-    <row r="99" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI98" s="4"/>
+      <c r="BJ98" s="4"/>
+      <c r="BK98" s="4"/>
+      <c r="BL98" s="4"/>
+    </row>
+    <row r="99" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -7616,8 +8093,12 @@
       <c r="BF99" s="4"/>
       <c r="BG99" s="4"/>
       <c r="BH99" s="4"/>
-    </row>
-    <row r="100" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI99" s="4"/>
+      <c r="BJ99" s="4"/>
+      <c r="BK99" s="4"/>
+      <c r="BL99" s="4"/>
+    </row>
+    <row r="100" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -7676,8 +8157,12 @@
       <c r="BF100" s="4"/>
       <c r="BG100" s="4"/>
       <c r="BH100" s="4"/>
-    </row>
-    <row r="101" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI100" s="4"/>
+      <c r="BJ100" s="4"/>
+      <c r="BK100" s="4"/>
+      <c r="BL100" s="4"/>
+    </row>
+    <row r="101" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -7736,8 +8221,12 @@
       <c r="BF101" s="4"/>
       <c r="BG101" s="4"/>
       <c r="BH101" s="4"/>
-    </row>
-    <row r="102" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI101" s="4"/>
+      <c r="BJ101" s="4"/>
+      <c r="BK101" s="4"/>
+      <c r="BL101" s="4"/>
+    </row>
+    <row r="102" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -7796,8 +8285,12 @@
       <c r="BF102" s="4"/>
       <c r="BG102" s="4"/>
       <c r="BH102" s="4"/>
-    </row>
-    <row r="103" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI102" s="4"/>
+      <c r="BJ102" s="4"/>
+      <c r="BK102" s="4"/>
+      <c r="BL102" s="4"/>
+    </row>
+    <row r="103" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -7856,8 +8349,12 @@
       <c r="BF103" s="4"/>
       <c r="BG103" s="4"/>
       <c r="BH103" s="4"/>
-    </row>
-    <row r="104" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI103" s="4"/>
+      <c r="BJ103" s="4"/>
+      <c r="BK103" s="4"/>
+      <c r="BL103" s="4"/>
+    </row>
+    <row r="104" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -7916,8 +8413,12 @@
       <c r="BF104" s="4"/>
       <c r="BG104" s="4"/>
       <c r="BH104" s="4"/>
-    </row>
-    <row r="105" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI104" s="4"/>
+      <c r="BJ104" s="4"/>
+      <c r="BK104" s="4"/>
+      <c r="BL104" s="4"/>
+    </row>
+    <row r="105" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -7976,8 +8477,12 @@
       <c r="BF105" s="4"/>
       <c r="BG105" s="4"/>
       <c r="BH105" s="4"/>
-    </row>
-    <row r="106" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI105" s="4"/>
+      <c r="BJ105" s="4"/>
+      <c r="BK105" s="4"/>
+      <c r="BL105" s="4"/>
+    </row>
+    <row r="106" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -8036,8 +8541,12 @@
       <c r="BF106" s="4"/>
       <c r="BG106" s="4"/>
       <c r="BH106" s="4"/>
-    </row>
-    <row r="107" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI106" s="4"/>
+      <c r="BJ106" s="4"/>
+      <c r="BK106" s="4"/>
+      <c r="BL106" s="4"/>
+    </row>
+    <row r="107" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -8096,8 +8605,12 @@
       <c r="BF107" s="4"/>
       <c r="BG107" s="4"/>
       <c r="BH107" s="4"/>
-    </row>
-    <row r="108" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI107" s="4"/>
+      <c r="BJ107" s="4"/>
+      <c r="BK107" s="4"/>
+      <c r="BL107" s="4"/>
+    </row>
+    <row r="108" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -8156,8 +8669,12 @@
       <c r="BF108" s="4"/>
       <c r="BG108" s="4"/>
       <c r="BH108" s="4"/>
-    </row>
-    <row r="109" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI108" s="4"/>
+      <c r="BJ108" s="4"/>
+      <c r="BK108" s="4"/>
+      <c r="BL108" s="4"/>
+    </row>
+    <row r="109" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
@@ -8216,8 +8733,12 @@
       <c r="BF109" s="4"/>
       <c r="BG109" s="4"/>
       <c r="BH109" s="4"/>
-    </row>
-    <row r="110" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI109" s="4"/>
+      <c r="BJ109" s="4"/>
+      <c r="BK109" s="4"/>
+      <c r="BL109" s="4"/>
+    </row>
+    <row r="110" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
@@ -8276,8 +8797,12 @@
       <c r="BF110" s="4"/>
       <c r="BG110" s="4"/>
       <c r="BH110" s="4"/>
-    </row>
-    <row r="111" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI110" s="4"/>
+      <c r="BJ110" s="4"/>
+      <c r="BK110" s="4"/>
+      <c r="BL110" s="4"/>
+    </row>
+    <row r="111" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
@@ -8336,8 +8861,12 @@
       <c r="BF111" s="4"/>
       <c r="BG111" s="4"/>
       <c r="BH111" s="4"/>
-    </row>
-    <row r="112" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI111" s="4"/>
+      <c r="BJ111" s="4"/>
+      <c r="BK111" s="4"/>
+      <c r="BL111" s="4"/>
+    </row>
+    <row r="112" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
@@ -8396,8 +8925,12 @@
       <c r="BF112" s="4"/>
       <c r="BG112" s="4"/>
       <c r="BH112" s="4"/>
-    </row>
-    <row r="113" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI112" s="4"/>
+      <c r="BJ112" s="4"/>
+      <c r="BK112" s="4"/>
+      <c r="BL112" s="4"/>
+    </row>
+    <row r="113" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -8456,8 +8989,12 @@
       <c r="BF113" s="4"/>
       <c r="BG113" s="4"/>
       <c r="BH113" s="4"/>
-    </row>
-    <row r="114" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI113" s="4"/>
+      <c r="BJ113" s="4"/>
+      <c r="BK113" s="4"/>
+      <c r="BL113" s="4"/>
+    </row>
+    <row r="114" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -8516,8 +9053,12 @@
       <c r="BF114" s="4"/>
       <c r="BG114" s="4"/>
       <c r="BH114" s="4"/>
-    </row>
-    <row r="115" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI114" s="4"/>
+      <c r="BJ114" s="4"/>
+      <c r="BK114" s="4"/>
+      <c r="BL114" s="4"/>
+    </row>
+    <row r="115" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -8576,8 +9117,12 @@
       <c r="BF115" s="4"/>
       <c r="BG115" s="4"/>
       <c r="BH115" s="4"/>
-    </row>
-    <row r="116" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI115" s="4"/>
+      <c r="BJ115" s="4"/>
+      <c r="BK115" s="4"/>
+      <c r="BL115" s="4"/>
+    </row>
+    <row r="116" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -8636,8 +9181,12 @@
       <c r="BF116" s="4"/>
       <c r="BG116" s="4"/>
       <c r="BH116" s="4"/>
-    </row>
-    <row r="117" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI116" s="4"/>
+      <c r="BJ116" s="4"/>
+      <c r="BK116" s="4"/>
+      <c r="BL116" s="4"/>
+    </row>
+    <row r="117" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -8696,8 +9245,12 @@
       <c r="BF117" s="4"/>
       <c r="BG117" s="4"/>
       <c r="BH117" s="4"/>
-    </row>
-    <row r="118" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI117" s="4"/>
+      <c r="BJ117" s="4"/>
+      <c r="BK117" s="4"/>
+      <c r="BL117" s="4"/>
+    </row>
+    <row r="118" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -8756,8 +9309,12 @@
       <c r="BF118" s="4"/>
       <c r="BG118" s="4"/>
       <c r="BH118" s="4"/>
-    </row>
-    <row r="119" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI118" s="4"/>
+      <c r="BJ118" s="4"/>
+      <c r="BK118" s="4"/>
+      <c r="BL118" s="4"/>
+    </row>
+    <row r="119" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -8816,8 +9373,12 @@
       <c r="BF119" s="4"/>
       <c r="BG119" s="4"/>
       <c r="BH119" s="4"/>
-    </row>
-    <row r="120" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI119" s="4"/>
+      <c r="BJ119" s="4"/>
+      <c r="BK119" s="4"/>
+      <c r="BL119" s="4"/>
+    </row>
+    <row r="120" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -8876,8 +9437,12 @@
       <c r="BF120" s="4"/>
       <c r="BG120" s="4"/>
       <c r="BH120" s="4"/>
-    </row>
-    <row r="121" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI120" s="4"/>
+      <c r="BJ120" s="4"/>
+      <c r="BK120" s="4"/>
+      <c r="BL120" s="4"/>
+    </row>
+    <row r="121" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
@@ -8936,8 +9501,12 @@
       <c r="BF121" s="4"/>
       <c r="BG121" s="4"/>
       <c r="BH121" s="4"/>
-    </row>
-    <row r="122" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI121" s="4"/>
+      <c r="BJ121" s="4"/>
+      <c r="BK121" s="4"/>
+      <c r="BL121" s="4"/>
+    </row>
+    <row r="122" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
@@ -8996,8 +9565,12 @@
       <c r="BF122" s="4"/>
       <c r="BG122" s="4"/>
       <c r="BH122" s="4"/>
-    </row>
-    <row r="123" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI122" s="4"/>
+      <c r="BJ122" s="4"/>
+      <c r="BK122" s="4"/>
+      <c r="BL122" s="4"/>
+    </row>
+    <row r="123" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
@@ -9056,8 +9629,12 @@
       <c r="BF123" s="4"/>
       <c r="BG123" s="4"/>
       <c r="BH123" s="4"/>
-    </row>
-    <row r="124" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI123" s="4"/>
+      <c r="BJ123" s="4"/>
+      <c r="BK123" s="4"/>
+      <c r="BL123" s="4"/>
+    </row>
+    <row r="124" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -9116,8 +9693,12 @@
       <c r="BF124" s="4"/>
       <c r="BG124" s="4"/>
       <c r="BH124" s="4"/>
-    </row>
-    <row r="125" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI124" s="4"/>
+      <c r="BJ124" s="4"/>
+      <c r="BK124" s="4"/>
+      <c r="BL124" s="4"/>
+    </row>
+    <row r="125" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -9176,8 +9757,12 @@
       <c r="BF125" s="4"/>
       <c r="BG125" s="4"/>
       <c r="BH125" s="4"/>
-    </row>
-    <row r="126" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI125" s="4"/>
+      <c r="BJ125" s="4"/>
+      <c r="BK125" s="4"/>
+      <c r="BL125" s="4"/>
+    </row>
+    <row r="126" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -9236,8 +9821,12 @@
       <c r="BF126" s="4"/>
       <c r="BG126" s="4"/>
       <c r="BH126" s="4"/>
-    </row>
-    <row r="127" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI126" s="4"/>
+      <c r="BJ126" s="4"/>
+      <c r="BK126" s="4"/>
+      <c r="BL126" s="4"/>
+    </row>
+    <row r="127" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -9296,8 +9885,12 @@
       <c r="BF127" s="4"/>
       <c r="BG127" s="4"/>
       <c r="BH127" s="4"/>
-    </row>
-    <row r="128" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI127" s="4"/>
+      <c r="BJ127" s="4"/>
+      <c r="BK127" s="4"/>
+      <c r="BL127" s="4"/>
+    </row>
+    <row r="128" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -9356,8 +9949,12 @@
       <c r="BF128" s="4"/>
       <c r="BG128" s="4"/>
       <c r="BH128" s="4"/>
-    </row>
-    <row r="129" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI128" s="4"/>
+      <c r="BJ128" s="4"/>
+      <c r="BK128" s="4"/>
+      <c r="BL128" s="4"/>
+    </row>
+    <row r="129" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -9416,8 +10013,12 @@
       <c r="BF129" s="4"/>
       <c r="BG129" s="4"/>
       <c r="BH129" s="4"/>
-    </row>
-    <row r="130" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI129" s="4"/>
+      <c r="BJ129" s="4"/>
+      <c r="BK129" s="4"/>
+      <c r="BL129" s="4"/>
+    </row>
+    <row r="130" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -9476,8 +10077,12 @@
       <c r="BF130" s="4"/>
       <c r="BG130" s="4"/>
       <c r="BH130" s="4"/>
-    </row>
-    <row r="131" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI130" s="4"/>
+      <c r="BJ130" s="4"/>
+      <c r="BK130" s="4"/>
+      <c r="BL130" s="4"/>
+    </row>
+    <row r="131" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
@@ -9536,8 +10141,12 @@
       <c r="BF131" s="4"/>
       <c r="BG131" s="4"/>
       <c r="BH131" s="4"/>
-    </row>
-    <row r="132" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI131" s="4"/>
+      <c r="BJ131" s="4"/>
+      <c r="BK131" s="4"/>
+      <c r="BL131" s="4"/>
+    </row>
+    <row r="132" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
@@ -9596,8 +10205,12 @@
       <c r="BF132" s="4"/>
       <c r="BG132" s="4"/>
       <c r="BH132" s="4"/>
-    </row>
-    <row r="133" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI132" s="4"/>
+      <c r="BJ132" s="4"/>
+      <c r="BK132" s="4"/>
+      <c r="BL132" s="4"/>
+    </row>
+    <row r="133" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
@@ -9656,8 +10269,12 @@
       <c r="BF133" s="4"/>
       <c r="BG133" s="4"/>
       <c r="BH133" s="4"/>
-    </row>
-    <row r="134" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI133" s="4"/>
+      <c r="BJ133" s="4"/>
+      <c r="BK133" s="4"/>
+      <c r="BL133" s="4"/>
+    </row>
+    <row r="134" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
@@ -9716,8 +10333,12 @@
       <c r="BF134" s="4"/>
       <c r="BG134" s="4"/>
       <c r="BH134" s="4"/>
-    </row>
-    <row r="135" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI134" s="4"/>
+      <c r="BJ134" s="4"/>
+      <c r="BK134" s="4"/>
+      <c r="BL134" s="4"/>
+    </row>
+    <row r="135" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
@@ -9776,8 +10397,12 @@
       <c r="BF135" s="4"/>
       <c r="BG135" s="4"/>
       <c r="BH135" s="4"/>
-    </row>
-    <row r="136" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI135" s="4"/>
+      <c r="BJ135" s="4"/>
+      <c r="BK135" s="4"/>
+      <c r="BL135" s="4"/>
+    </row>
+    <row r="136" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
@@ -9836,8 +10461,12 @@
       <c r="BF136" s="4"/>
       <c r="BG136" s="4"/>
       <c r="BH136" s="4"/>
-    </row>
-    <row r="137" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI136" s="4"/>
+      <c r="BJ136" s="4"/>
+      <c r="BK136" s="4"/>
+      <c r="BL136" s="4"/>
+    </row>
+    <row r="137" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
@@ -9896,8 +10525,12 @@
       <c r="BF137" s="4"/>
       <c r="BG137" s="4"/>
       <c r="BH137" s="4"/>
-    </row>
-    <row r="138" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI137" s="4"/>
+      <c r="BJ137" s="4"/>
+      <c r="BK137" s="4"/>
+      <c r="BL137" s="4"/>
+    </row>
+    <row r="138" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
@@ -9956,8 +10589,12 @@
       <c r="BF138" s="4"/>
       <c r="BG138" s="4"/>
       <c r="BH138" s="4"/>
-    </row>
-    <row r="139" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI138" s="4"/>
+      <c r="BJ138" s="4"/>
+      <c r="BK138" s="4"/>
+      <c r="BL138" s="4"/>
+    </row>
+    <row r="139" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
@@ -10016,8 +10653,12 @@
       <c r="BF139" s="4"/>
       <c r="BG139" s="4"/>
       <c r="BH139" s="4"/>
-    </row>
-    <row r="140" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI139" s="4"/>
+      <c r="BJ139" s="4"/>
+      <c r="BK139" s="4"/>
+      <c r="BL139" s="4"/>
+    </row>
+    <row r="140" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
@@ -10076,8 +10717,12 @@
       <c r="BF140" s="4"/>
       <c r="BG140" s="4"/>
       <c r="BH140" s="4"/>
-    </row>
-    <row r="141" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI140" s="4"/>
+      <c r="BJ140" s="4"/>
+      <c r="BK140" s="4"/>
+      <c r="BL140" s="4"/>
+    </row>
+    <row r="141" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
@@ -10136,8 +10781,12 @@
       <c r="BF141" s="4"/>
       <c r="BG141" s="4"/>
       <c r="BH141" s="4"/>
-    </row>
-    <row r="142" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI141" s="4"/>
+      <c r="BJ141" s="4"/>
+      <c r="BK141" s="4"/>
+      <c r="BL141" s="4"/>
+    </row>
+    <row r="142" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
@@ -10196,8 +10845,12 @@
       <c r="BF142" s="4"/>
       <c r="BG142" s="4"/>
       <c r="BH142" s="4"/>
-    </row>
-    <row r="143" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI142" s="4"/>
+      <c r="BJ142" s="4"/>
+      <c r="BK142" s="4"/>
+      <c r="BL142" s="4"/>
+    </row>
+    <row r="143" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
@@ -10256,8 +10909,12 @@
       <c r="BF143" s="4"/>
       <c r="BG143" s="4"/>
       <c r="BH143" s="4"/>
-    </row>
-    <row r="144" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI143" s="4"/>
+      <c r="BJ143" s="4"/>
+      <c r="BK143" s="4"/>
+      <c r="BL143" s="4"/>
+    </row>
+    <row r="144" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
@@ -10316,8 +10973,12 @@
       <c r="BF144" s="4"/>
       <c r="BG144" s="4"/>
       <c r="BH144" s="4"/>
-    </row>
-    <row r="145" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI144" s="4"/>
+      <c r="BJ144" s="4"/>
+      <c r="BK144" s="4"/>
+      <c r="BL144" s="4"/>
+    </row>
+    <row r="145" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
@@ -10376,8 +11037,12 @@
       <c r="BF145" s="4"/>
       <c r="BG145" s="4"/>
       <c r="BH145" s="4"/>
-    </row>
-    <row r="146" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI145" s="4"/>
+      <c r="BJ145" s="4"/>
+      <c r="BK145" s="4"/>
+      <c r="BL145" s="4"/>
+    </row>
+    <row r="146" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
@@ -10436,8 +11101,12 @@
       <c r="BF146" s="4"/>
       <c r="BG146" s="4"/>
       <c r="BH146" s="4"/>
-    </row>
-    <row r="147" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI146" s="4"/>
+      <c r="BJ146" s="4"/>
+      <c r="BK146" s="4"/>
+      <c r="BL146" s="4"/>
+    </row>
+    <row r="147" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
@@ -10496,8 +11165,12 @@
       <c r="BF147" s="4"/>
       <c r="BG147" s="4"/>
       <c r="BH147" s="4"/>
-    </row>
-    <row r="148" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI147" s="4"/>
+      <c r="BJ147" s="4"/>
+      <c r="BK147" s="4"/>
+      <c r="BL147" s="4"/>
+    </row>
+    <row r="148" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
@@ -10556,8 +11229,12 @@
       <c r="BF148" s="4"/>
       <c r="BG148" s="4"/>
       <c r="BH148" s="4"/>
-    </row>
-    <row r="149" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI148" s="4"/>
+      <c r="BJ148" s="4"/>
+      <c r="BK148" s="4"/>
+      <c r="BL148" s="4"/>
+    </row>
+    <row r="149" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
@@ -10616,8 +11293,12 @@
       <c r="BF149" s="4"/>
       <c r="BG149" s="4"/>
       <c r="BH149" s="4"/>
-    </row>
-    <row r="150" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI149" s="4"/>
+      <c r="BJ149" s="4"/>
+      <c r="BK149" s="4"/>
+      <c r="BL149" s="4"/>
+    </row>
+    <row r="150" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
@@ -10676,8 +11357,12 @@
       <c r="BF150" s="4"/>
       <c r="BG150" s="4"/>
       <c r="BH150" s="4"/>
-    </row>
-    <row r="151" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI150" s="4"/>
+      <c r="BJ150" s="4"/>
+      <c r="BK150" s="4"/>
+      <c r="BL150" s="4"/>
+    </row>
+    <row r="151" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
@@ -10736,8 +11421,12 @@
       <c r="BF151" s="4"/>
       <c r="BG151" s="4"/>
       <c r="BH151" s="4"/>
-    </row>
-    <row r="152" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI151" s="4"/>
+      <c r="BJ151" s="4"/>
+      <c r="BK151" s="4"/>
+      <c r="BL151" s="4"/>
+    </row>
+    <row r="152" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -10796,8 +11485,12 @@
       <c r="BF152" s="4"/>
       <c r="BG152" s="4"/>
       <c r="BH152" s="4"/>
-    </row>
-    <row r="153" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI152" s="4"/>
+      <c r="BJ152" s="4"/>
+      <c r="BK152" s="4"/>
+      <c r="BL152" s="4"/>
+    </row>
+    <row r="153" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
@@ -10856,8 +11549,12 @@
       <c r="BF153" s="4"/>
       <c r="BG153" s="4"/>
       <c r="BH153" s="4"/>
-    </row>
-    <row r="154" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI153" s="4"/>
+      <c r="BJ153" s="4"/>
+      <c r="BK153" s="4"/>
+      <c r="BL153" s="4"/>
+    </row>
+    <row r="154" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
@@ -10916,8 +11613,12 @@
       <c r="BF154" s="4"/>
       <c r="BG154" s="4"/>
       <c r="BH154" s="4"/>
-    </row>
-    <row r="155" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI154" s="4"/>
+      <c r="BJ154" s="4"/>
+      <c r="BK154" s="4"/>
+      <c r="BL154" s="4"/>
+    </row>
+    <row r="155" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
@@ -10976,8 +11677,12 @@
       <c r="BF155" s="4"/>
       <c r="BG155" s="4"/>
       <c r="BH155" s="4"/>
-    </row>
-    <row r="156" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI155" s="4"/>
+      <c r="BJ155" s="4"/>
+      <c r="BK155" s="4"/>
+      <c r="BL155" s="4"/>
+    </row>
+    <row r="156" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
@@ -11036,8 +11741,12 @@
       <c r="BF156" s="4"/>
       <c r="BG156" s="4"/>
       <c r="BH156" s="4"/>
-    </row>
-    <row r="157" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI156" s="4"/>
+      <c r="BJ156" s="4"/>
+      <c r="BK156" s="4"/>
+      <c r="BL156" s="4"/>
+    </row>
+    <row r="157" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
@@ -11096,8 +11805,12 @@
       <c r="BF157" s="4"/>
       <c r="BG157" s="4"/>
       <c r="BH157" s="4"/>
-    </row>
-    <row r="158" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI157" s="4"/>
+      <c r="BJ157" s="4"/>
+      <c r="BK157" s="4"/>
+      <c r="BL157" s="4"/>
+    </row>
+    <row r="158" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -11156,8 +11869,12 @@
       <c r="BF158" s="4"/>
       <c r="BG158" s="4"/>
       <c r="BH158" s="4"/>
-    </row>
-    <row r="159" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI158" s="4"/>
+      <c r="BJ158" s="4"/>
+      <c r="BK158" s="4"/>
+      <c r="BL158" s="4"/>
+    </row>
+    <row r="159" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -11216,8 +11933,12 @@
       <c r="BF159" s="4"/>
       <c r="BG159" s="4"/>
       <c r="BH159" s="4"/>
-    </row>
-    <row r="160" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI159" s="4"/>
+      <c r="BJ159" s="4"/>
+      <c r="BK159" s="4"/>
+      <c r="BL159" s="4"/>
+    </row>
+    <row r="160" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
@@ -11276,8 +11997,12 @@
       <c r="BF160" s="4"/>
       <c r="BG160" s="4"/>
       <c r="BH160" s="4"/>
-    </row>
-    <row r="161" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI160" s="4"/>
+      <c r="BJ160" s="4"/>
+      <c r="BK160" s="4"/>
+      <c r="BL160" s="4"/>
+    </row>
+    <row r="161" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
@@ -11336,8 +12061,12 @@
       <c r="BF161" s="4"/>
       <c r="BG161" s="4"/>
       <c r="BH161" s="4"/>
-    </row>
-    <row r="162" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI161" s="4"/>
+      <c r="BJ161" s="4"/>
+      <c r="BK161" s="4"/>
+      <c r="BL161" s="4"/>
+    </row>
+    <row r="162" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -11396,8 +12125,12 @@
       <c r="BF162" s="4"/>
       <c r="BG162" s="4"/>
       <c r="BH162" s="4"/>
-    </row>
-    <row r="163" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI162" s="4"/>
+      <c r="BJ162" s="4"/>
+      <c r="BK162" s="4"/>
+      <c r="BL162" s="4"/>
+    </row>
+    <row r="163" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -11456,8 +12189,12 @@
       <c r="BF163" s="4"/>
       <c r="BG163" s="4"/>
       <c r="BH163" s="4"/>
-    </row>
-    <row r="164" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI163" s="4"/>
+      <c r="BJ163" s="4"/>
+      <c r="BK163" s="4"/>
+      <c r="BL163" s="4"/>
+    </row>
+    <row r="164" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
@@ -11516,8 +12253,12 @@
       <c r="BF164" s="4"/>
       <c r="BG164" s="4"/>
       <c r="BH164" s="4"/>
-    </row>
-    <row r="165" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI164" s="4"/>
+      <c r="BJ164" s="4"/>
+      <c r="BK164" s="4"/>
+      <c r="BL164" s="4"/>
+    </row>
+    <row r="165" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
@@ -11576,8 +12317,12 @@
       <c r="BF165" s="4"/>
       <c r="BG165" s="4"/>
       <c r="BH165" s="4"/>
-    </row>
-    <row r="166" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI165" s="4"/>
+      <c r="BJ165" s="4"/>
+      <c r="BK165" s="4"/>
+      <c r="BL165" s="4"/>
+    </row>
+    <row r="166" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -11636,8 +12381,12 @@
       <c r="BF166" s="4"/>
       <c r="BG166" s="4"/>
       <c r="BH166" s="4"/>
-    </row>
-    <row r="167" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI166" s="4"/>
+      <c r="BJ166" s="4"/>
+      <c r="BK166" s="4"/>
+      <c r="BL166" s="4"/>
+    </row>
+    <row r="167" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
@@ -11696,8 +12445,12 @@
       <c r="BF167" s="4"/>
       <c r="BG167" s="4"/>
       <c r="BH167" s="4"/>
-    </row>
-    <row r="168" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI167" s="4"/>
+      <c r="BJ167" s="4"/>
+      <c r="BK167" s="4"/>
+      <c r="BL167" s="4"/>
+    </row>
+    <row r="168" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -11756,8 +12509,12 @@
       <c r="BF168" s="4"/>
       <c r="BG168" s="4"/>
       <c r="BH168" s="4"/>
-    </row>
-    <row r="169" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI168" s="4"/>
+      <c r="BJ168" s="4"/>
+      <c r="BK168" s="4"/>
+      <c r="BL168" s="4"/>
+    </row>
+    <row r="169" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
@@ -11816,8 +12573,12 @@
       <c r="BF169" s="4"/>
       <c r="BG169" s="4"/>
       <c r="BH169" s="4"/>
-    </row>
-    <row r="170" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI169" s="4"/>
+      <c r="BJ169" s="4"/>
+      <c r="BK169" s="4"/>
+      <c r="BL169" s="4"/>
+    </row>
+    <row r="170" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -11876,8 +12637,12 @@
       <c r="BF170" s="4"/>
       <c r="BG170" s="4"/>
       <c r="BH170" s="4"/>
-    </row>
-    <row r="171" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI170" s="4"/>
+      <c r="BJ170" s="4"/>
+      <c r="BK170" s="4"/>
+      <c r="BL170" s="4"/>
+    </row>
+    <row r="171" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -11936,8 +12701,12 @@
       <c r="BF171" s="4"/>
       <c r="BG171" s="4"/>
       <c r="BH171" s="4"/>
-    </row>
-    <row r="172" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI171" s="4"/>
+      <c r="BJ171" s="4"/>
+      <c r="BK171" s="4"/>
+      <c r="BL171" s="4"/>
+    </row>
+    <row r="172" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
@@ -11996,8 +12765,12 @@
       <c r="BF172" s="4"/>
       <c r="BG172" s="4"/>
       <c r="BH172" s="4"/>
-    </row>
-    <row r="173" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI172" s="4"/>
+      <c r="BJ172" s="4"/>
+      <c r="BK172" s="4"/>
+      <c r="BL172" s="4"/>
+    </row>
+    <row r="173" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -12056,8 +12829,12 @@
       <c r="BF173" s="4"/>
       <c r="BG173" s="4"/>
       <c r="BH173" s="4"/>
-    </row>
-    <row r="174" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI173" s="4"/>
+      <c r="BJ173" s="4"/>
+      <c r="BK173" s="4"/>
+      <c r="BL173" s="4"/>
+    </row>
+    <row r="174" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -12116,8 +12893,12 @@
       <c r="BF174" s="4"/>
       <c r="BG174" s="4"/>
       <c r="BH174" s="4"/>
-    </row>
-    <row r="175" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI174" s="4"/>
+      <c r="BJ174" s="4"/>
+      <c r="BK174" s="4"/>
+      <c r="BL174" s="4"/>
+    </row>
+    <row r="175" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -12176,8 +12957,12 @@
       <c r="BF175" s="4"/>
       <c r="BG175" s="4"/>
       <c r="BH175" s="4"/>
-    </row>
-    <row r="176" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI175" s="4"/>
+      <c r="BJ175" s="4"/>
+      <c r="BK175" s="4"/>
+      <c r="BL175" s="4"/>
+    </row>
+    <row r="176" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -12236,8 +13021,12 @@
       <c r="BF176" s="4"/>
       <c r="BG176" s="4"/>
       <c r="BH176" s="4"/>
-    </row>
-    <row r="177" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI176" s="4"/>
+      <c r="BJ176" s="4"/>
+      <c r="BK176" s="4"/>
+      <c r="BL176" s="4"/>
+    </row>
+    <row r="177" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -12296,8 +13085,12 @@
       <c r="BF177" s="4"/>
       <c r="BG177" s="4"/>
       <c r="BH177" s="4"/>
-    </row>
-    <row r="178" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI177" s="4"/>
+      <c r="BJ177" s="4"/>
+      <c r="BK177" s="4"/>
+      <c r="BL177" s="4"/>
+    </row>
+    <row r="178" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -12356,8 +13149,12 @@
       <c r="BF178" s="4"/>
       <c r="BG178" s="4"/>
       <c r="BH178" s="4"/>
-    </row>
-    <row r="179" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI178" s="4"/>
+      <c r="BJ178" s="4"/>
+      <c r="BK178" s="4"/>
+      <c r="BL178" s="4"/>
+    </row>
+    <row r="179" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -12416,8 +13213,12 @@
       <c r="BF179" s="4"/>
       <c r="BG179" s="4"/>
       <c r="BH179" s="4"/>
-    </row>
-    <row r="180" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI179" s="4"/>
+      <c r="BJ179" s="4"/>
+      <c r="BK179" s="4"/>
+      <c r="BL179" s="4"/>
+    </row>
+    <row r="180" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
@@ -12476,8 +13277,12 @@
       <c r="BF180" s="4"/>
       <c r="BG180" s="4"/>
       <c r="BH180" s="4"/>
-    </row>
-    <row r="181" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI180" s="4"/>
+      <c r="BJ180" s="4"/>
+      <c r="BK180" s="4"/>
+      <c r="BL180" s="4"/>
+    </row>
+    <row r="181" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -12536,8 +13341,12 @@
       <c r="BF181" s="4"/>
       <c r="BG181" s="4"/>
       <c r="BH181" s="4"/>
-    </row>
-    <row r="182" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI181" s="4"/>
+      <c r="BJ181" s="4"/>
+      <c r="BK181" s="4"/>
+      <c r="BL181" s="4"/>
+    </row>
+    <row r="182" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -12596,8 +13405,12 @@
       <c r="BF182" s="4"/>
       <c r="BG182" s="4"/>
       <c r="BH182" s="4"/>
-    </row>
-    <row r="183" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI182" s="4"/>
+      <c r="BJ182" s="4"/>
+      <c r="BK182" s="4"/>
+      <c r="BL182" s="4"/>
+    </row>
+    <row r="183" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -12656,8 +13469,12 @@
       <c r="BF183" s="4"/>
       <c r="BG183" s="4"/>
       <c r="BH183" s="4"/>
-    </row>
-    <row r="184" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI183" s="4"/>
+      <c r="BJ183" s="4"/>
+      <c r="BK183" s="4"/>
+      <c r="BL183" s="4"/>
+    </row>
+    <row r="184" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
@@ -12716,8 +13533,12 @@
       <c r="BF184" s="4"/>
       <c r="BG184" s="4"/>
       <c r="BH184" s="4"/>
-    </row>
-    <row r="185" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI184" s="4"/>
+      <c r="BJ184" s="4"/>
+      <c r="BK184" s="4"/>
+      <c r="BL184" s="4"/>
+    </row>
+    <row r="185" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
@@ -12776,8 +13597,12 @@
       <c r="BF185" s="4"/>
       <c r="BG185" s="4"/>
       <c r="BH185" s="4"/>
-    </row>
-    <row r="186" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI185" s="4"/>
+      <c r="BJ185" s="4"/>
+      <c r="BK185" s="4"/>
+      <c r="BL185" s="4"/>
+    </row>
+    <row r="186" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
@@ -12836,8 +13661,12 @@
       <c r="BF186" s="4"/>
       <c r="BG186" s="4"/>
       <c r="BH186" s="4"/>
-    </row>
-    <row r="187" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI186" s="4"/>
+      <c r="BJ186" s="4"/>
+      <c r="BK186" s="4"/>
+      <c r="BL186" s="4"/>
+    </row>
+    <row r="187" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -12896,8 +13725,12 @@
       <c r="BF187" s="4"/>
       <c r="BG187" s="4"/>
       <c r="BH187" s="4"/>
-    </row>
-    <row r="188" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI187" s="4"/>
+      <c r="BJ187" s="4"/>
+      <c r="BK187" s="4"/>
+      <c r="BL187" s="4"/>
+    </row>
+    <row r="188" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -12956,8 +13789,12 @@
       <c r="BF188" s="4"/>
       <c r="BG188" s="4"/>
       <c r="BH188" s="4"/>
-    </row>
-    <row r="189" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI188" s="4"/>
+      <c r="BJ188" s="4"/>
+      <c r="BK188" s="4"/>
+      <c r="BL188" s="4"/>
+    </row>
+    <row r="189" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -13016,8 +13853,12 @@
       <c r="BF189" s="4"/>
       <c r="BG189" s="4"/>
       <c r="BH189" s="4"/>
-    </row>
-    <row r="190" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI189" s="4"/>
+      <c r="BJ189" s="4"/>
+      <c r="BK189" s="4"/>
+      <c r="BL189" s="4"/>
+    </row>
+    <row r="190" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
@@ -13076,8 +13917,12 @@
       <c r="BF190" s="4"/>
       <c r="BG190" s="4"/>
       <c r="BH190" s="4"/>
-    </row>
-    <row r="191" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI190" s="4"/>
+      <c r="BJ190" s="4"/>
+      <c r="BK190" s="4"/>
+      <c r="BL190" s="4"/>
+    </row>
+    <row r="191" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -13136,8 +13981,12 @@
       <c r="BF191" s="4"/>
       <c r="BG191" s="4"/>
       <c r="BH191" s="4"/>
-    </row>
-    <row r="192" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI191" s="4"/>
+      <c r="BJ191" s="4"/>
+      <c r="BK191" s="4"/>
+      <c r="BL191" s="4"/>
+    </row>
+    <row r="192" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -13196,8 +14045,12 @@
       <c r="BF192" s="4"/>
       <c r="BG192" s="4"/>
       <c r="BH192" s="4"/>
-    </row>
-    <row r="193" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI192" s="4"/>
+      <c r="BJ192" s="4"/>
+      <c r="BK192" s="4"/>
+      <c r="BL192" s="4"/>
+    </row>
+    <row r="193" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -13256,8 +14109,12 @@
       <c r="BF193" s="4"/>
       <c r="BG193" s="4"/>
       <c r="BH193" s="4"/>
-    </row>
-    <row r="194" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI193" s="4"/>
+      <c r="BJ193" s="4"/>
+      <c r="BK193" s="4"/>
+      <c r="BL193" s="4"/>
+    </row>
+    <row r="194" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -13316,8 +14173,12 @@
       <c r="BF194" s="4"/>
       <c r="BG194" s="4"/>
       <c r="BH194" s="4"/>
-    </row>
-    <row r="195" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI194" s="4"/>
+      <c r="BJ194" s="4"/>
+      <c r="BK194" s="4"/>
+      <c r="BL194" s="4"/>
+    </row>
+    <row r="195" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
@@ -13376,8 +14237,12 @@
       <c r="BF195" s="4"/>
       <c r="BG195" s="4"/>
       <c r="BH195" s="4"/>
-    </row>
-    <row r="196" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI195" s="4"/>
+      <c r="BJ195" s="4"/>
+      <c r="BK195" s="4"/>
+      <c r="BL195" s="4"/>
+    </row>
+    <row r="196" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
@@ -13436,8 +14301,12 @@
       <c r="BF196" s="4"/>
       <c r="BG196" s="4"/>
       <c r="BH196" s="4"/>
-    </row>
-    <row r="197" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI196" s="4"/>
+      <c r="BJ196" s="4"/>
+      <c r="BK196" s="4"/>
+      <c r="BL196" s="4"/>
+    </row>
+    <row r="197" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
@@ -13496,8 +14365,12 @@
       <c r="BF197" s="4"/>
       <c r="BG197" s="4"/>
       <c r="BH197" s="4"/>
-    </row>
-    <row r="198" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI197" s="4"/>
+      <c r="BJ197" s="4"/>
+      <c r="BK197" s="4"/>
+      <c r="BL197" s="4"/>
+    </row>
+    <row r="198" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
@@ -13556,8 +14429,12 @@
       <c r="BF198" s="4"/>
       <c r="BG198" s="4"/>
       <c r="BH198" s="4"/>
-    </row>
-    <row r="199" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI198" s="4"/>
+      <c r="BJ198" s="4"/>
+      <c r="BK198" s="4"/>
+      <c r="BL198" s="4"/>
+    </row>
+    <row r="199" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
@@ -13616,8 +14493,12 @@
       <c r="BF199" s="4"/>
       <c r="BG199" s="4"/>
       <c r="BH199" s="4"/>
-    </row>
-    <row r="200" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI199" s="4"/>
+      <c r="BJ199" s="4"/>
+      <c r="BK199" s="4"/>
+      <c r="BL199" s="4"/>
+    </row>
+    <row r="200" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
@@ -13676,8 +14557,12 @@
       <c r="BF200" s="4"/>
       <c r="BG200" s="4"/>
       <c r="BH200" s="4"/>
-    </row>
-    <row r="201" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI200" s="4"/>
+      <c r="BJ200" s="4"/>
+      <c r="BK200" s="4"/>
+      <c r="BL200" s="4"/>
+    </row>
+    <row r="201" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
@@ -13736,8 +14621,12 @@
       <c r="BF201" s="4"/>
       <c r="BG201" s="4"/>
       <c r="BH201" s="4"/>
-    </row>
-    <row r="202" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI201" s="4"/>
+      <c r="BJ201" s="4"/>
+      <c r="BK201" s="4"/>
+      <c r="BL201" s="4"/>
+    </row>
+    <row r="202" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
@@ -13796,8 +14685,12 @@
       <c r="BF202" s="4"/>
       <c r="BG202" s="4"/>
       <c r="BH202" s="4"/>
-    </row>
-    <row r="203" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI202" s="4"/>
+      <c r="BJ202" s="4"/>
+      <c r="BK202" s="4"/>
+      <c r="BL202" s="4"/>
+    </row>
+    <row r="203" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
@@ -13856,8 +14749,12 @@
       <c r="BF203" s="4"/>
       <c r="BG203" s="4"/>
       <c r="BH203" s="4"/>
-    </row>
-    <row r="204" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI203" s="4"/>
+      <c r="BJ203" s="4"/>
+      <c r="BK203" s="4"/>
+      <c r="BL203" s="4"/>
+    </row>
+    <row r="204" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
@@ -13916,8 +14813,12 @@
       <c r="BF204" s="4"/>
       <c r="BG204" s="4"/>
       <c r="BH204" s="4"/>
-    </row>
-    <row r="205" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI204" s="4"/>
+      <c r="BJ204" s="4"/>
+      <c r="BK204" s="4"/>
+      <c r="BL204" s="4"/>
+    </row>
+    <row r="205" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
@@ -13976,8 +14877,12 @@
       <c r="BF205" s="4"/>
       <c r="BG205" s="4"/>
       <c r="BH205" s="4"/>
-    </row>
-    <row r="206" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI205" s="4"/>
+      <c r="BJ205" s="4"/>
+      <c r="BK205" s="4"/>
+      <c r="BL205" s="4"/>
+    </row>
+    <row r="206" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
@@ -14036,8 +14941,12 @@
       <c r="BF206" s="4"/>
       <c r="BG206" s="4"/>
       <c r="BH206" s="4"/>
-    </row>
-    <row r="207" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI206" s="4"/>
+      <c r="BJ206" s="4"/>
+      <c r="BK206" s="4"/>
+      <c r="BL206" s="4"/>
+    </row>
+    <row r="207" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
@@ -14096,8 +15005,12 @@
       <c r="BF207" s="4"/>
       <c r="BG207" s="4"/>
       <c r="BH207" s="4"/>
-    </row>
-    <row r="208" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI207" s="4"/>
+      <c r="BJ207" s="4"/>
+      <c r="BK207" s="4"/>
+      <c r="BL207" s="4"/>
+    </row>
+    <row r="208" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
@@ -14156,8 +15069,12 @@
       <c r="BF208" s="4"/>
       <c r="BG208" s="4"/>
       <c r="BH208" s="4"/>
-    </row>
-    <row r="209" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI208" s="4"/>
+      <c r="BJ208" s="4"/>
+      <c r="BK208" s="4"/>
+      <c r="BL208" s="4"/>
+    </row>
+    <row r="209" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
@@ -14216,8 +15133,12 @@
       <c r="BF209" s="4"/>
       <c r="BG209" s="4"/>
       <c r="BH209" s="4"/>
-    </row>
-    <row r="210" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI209" s="4"/>
+      <c r="BJ209" s="4"/>
+      <c r="BK209" s="4"/>
+      <c r="BL209" s="4"/>
+    </row>
+    <row r="210" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
@@ -14276,8 +15197,12 @@
       <c r="BF210" s="4"/>
       <c r="BG210" s="4"/>
       <c r="BH210" s="4"/>
-    </row>
-    <row r="211" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI210" s="4"/>
+      <c r="BJ210" s="4"/>
+      <c r="BK210" s="4"/>
+      <c r="BL210" s="4"/>
+    </row>
+    <row r="211" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
@@ -14336,8 +15261,12 @@
       <c r="BF211" s="4"/>
       <c r="BG211" s="4"/>
       <c r="BH211" s="4"/>
-    </row>
-    <row r="212" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI211" s="4"/>
+      <c r="BJ211" s="4"/>
+      <c r="BK211" s="4"/>
+      <c r="BL211" s="4"/>
+    </row>
+    <row r="212" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
@@ -14396,8 +15325,12 @@
       <c r="BF212" s="4"/>
       <c r="BG212" s="4"/>
       <c r="BH212" s="4"/>
-    </row>
-    <row r="213" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI212" s="4"/>
+      <c r="BJ212" s="4"/>
+      <c r="BK212" s="4"/>
+      <c r="BL212" s="4"/>
+    </row>
+    <row r="213" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
@@ -14456,8 +15389,12 @@
       <c r="BF213" s="4"/>
       <c r="BG213" s="4"/>
       <c r="BH213" s="4"/>
-    </row>
-    <row r="214" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI213" s="4"/>
+      <c r="BJ213" s="4"/>
+      <c r="BK213" s="4"/>
+      <c r="BL213" s="4"/>
+    </row>
+    <row r="214" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
@@ -14516,8 +15453,12 @@
       <c r="BF214" s="4"/>
       <c r="BG214" s="4"/>
       <c r="BH214" s="4"/>
-    </row>
-    <row r="215" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI214" s="4"/>
+      <c r="BJ214" s="4"/>
+      <c r="BK214" s="4"/>
+      <c r="BL214" s="4"/>
+    </row>
+    <row r="215" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
@@ -14576,8 +15517,12 @@
       <c r="BF215" s="4"/>
       <c r="BG215" s="4"/>
       <c r="BH215" s="4"/>
-    </row>
-    <row r="216" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI215" s="4"/>
+      <c r="BJ215" s="4"/>
+      <c r="BK215" s="4"/>
+      <c r="BL215" s="4"/>
+    </row>
+    <row r="216" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
@@ -14636,8 +15581,12 @@
       <c r="BF216" s="4"/>
       <c r="BG216" s="4"/>
       <c r="BH216" s="4"/>
-    </row>
-    <row r="217" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI216" s="4"/>
+      <c r="BJ216" s="4"/>
+      <c r="BK216" s="4"/>
+      <c r="BL216" s="4"/>
+    </row>
+    <row r="217" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
@@ -14696,8 +15645,12 @@
       <c r="BF217" s="4"/>
       <c r="BG217" s="4"/>
       <c r="BH217" s="4"/>
-    </row>
-    <row r="218" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI217" s="4"/>
+      <c r="BJ217" s="4"/>
+      <c r="BK217" s="4"/>
+      <c r="BL217" s="4"/>
+    </row>
+    <row r="218" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
@@ -14756,8 +15709,12 @@
       <c r="BF218" s="4"/>
       <c r="BG218" s="4"/>
       <c r="BH218" s="4"/>
-    </row>
-    <row r="219" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI218" s="4"/>
+      <c r="BJ218" s="4"/>
+      <c r="BK218" s="4"/>
+      <c r="BL218" s="4"/>
+    </row>
+    <row r="219" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
@@ -14816,8 +15773,12 @@
       <c r="BF219" s="4"/>
       <c r="BG219" s="4"/>
       <c r="BH219" s="4"/>
-    </row>
-    <row r="220" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI219" s="4"/>
+      <c r="BJ219" s="4"/>
+      <c r="BK219" s="4"/>
+      <c r="BL219" s="4"/>
+    </row>
+    <row r="220" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
@@ -14876,8 +15837,12 @@
       <c r="BF220" s="4"/>
       <c r="BG220" s="4"/>
       <c r="BH220" s="4"/>
-    </row>
-    <row r="221" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI220" s="4"/>
+      <c r="BJ220" s="4"/>
+      <c r="BK220" s="4"/>
+      <c r="BL220" s="4"/>
+    </row>
+    <row r="221" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
@@ -14936,8 +15901,12 @@
       <c r="BF221" s="4"/>
       <c r="BG221" s="4"/>
       <c r="BH221" s="4"/>
-    </row>
-    <row r="222" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI221" s="4"/>
+      <c r="BJ221" s="4"/>
+      <c r="BK221" s="4"/>
+      <c r="BL221" s="4"/>
+    </row>
+    <row r="222" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
@@ -14996,8 +15965,12 @@
       <c r="BF222" s="4"/>
       <c r="BG222" s="4"/>
       <c r="BH222" s="4"/>
-    </row>
-    <row r="223" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI222" s="4"/>
+      <c r="BJ222" s="4"/>
+      <c r="BK222" s="4"/>
+      <c r="BL222" s="4"/>
+    </row>
+    <row r="223" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
@@ -15056,8 +16029,12 @@
       <c r="BF223" s="4"/>
       <c r="BG223" s="4"/>
       <c r="BH223" s="4"/>
-    </row>
-    <row r="224" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI223" s="4"/>
+      <c r="BJ223" s="4"/>
+      <c r="BK223" s="4"/>
+      <c r="BL223" s="4"/>
+    </row>
+    <row r="224" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
@@ -15116,8 +16093,12 @@
       <c r="BF224" s="4"/>
       <c r="BG224" s="4"/>
       <c r="BH224" s="4"/>
-    </row>
-    <row r="225" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI224" s="4"/>
+      <c r="BJ224" s="4"/>
+      <c r="BK224" s="4"/>
+      <c r="BL224" s="4"/>
+    </row>
+    <row r="225" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
@@ -15176,8 +16157,12 @@
       <c r="BF225" s="4"/>
       <c r="BG225" s="4"/>
       <c r="BH225" s="4"/>
-    </row>
-    <row r="226" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI225" s="4"/>
+      <c r="BJ225" s="4"/>
+      <c r="BK225" s="4"/>
+      <c r="BL225" s="4"/>
+    </row>
+    <row r="226" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
@@ -15236,8 +16221,12 @@
       <c r="BF226" s="4"/>
       <c r="BG226" s="4"/>
       <c r="BH226" s="4"/>
-    </row>
-    <row r="227" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI226" s="4"/>
+      <c r="BJ226" s="4"/>
+      <c r="BK226" s="4"/>
+      <c r="BL226" s="4"/>
+    </row>
+    <row r="227" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
@@ -15296,8 +16285,12 @@
       <c r="BF227" s="4"/>
       <c r="BG227" s="4"/>
       <c r="BH227" s="4"/>
-    </row>
-    <row r="228" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI227" s="4"/>
+      <c r="BJ227" s="4"/>
+      <c r="BK227" s="4"/>
+      <c r="BL227" s="4"/>
+    </row>
+    <row r="228" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
@@ -15356,8 +16349,12 @@
       <c r="BF228" s="4"/>
       <c r="BG228" s="4"/>
       <c r="BH228" s="4"/>
-    </row>
-    <row r="229" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI228" s="4"/>
+      <c r="BJ228" s="4"/>
+      <c r="BK228" s="4"/>
+      <c r="BL228" s="4"/>
+    </row>
+    <row r="229" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
@@ -15416,8 +16413,12 @@
       <c r="BF229" s="4"/>
       <c r="BG229" s="4"/>
       <c r="BH229" s="4"/>
-    </row>
-    <row r="230" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI229" s="4"/>
+      <c r="BJ229" s="4"/>
+      <c r="BK229" s="4"/>
+      <c r="BL229" s="4"/>
+    </row>
+    <row r="230" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
@@ -15476,8 +16477,12 @@
       <c r="BF230" s="4"/>
       <c r="BG230" s="4"/>
       <c r="BH230" s="4"/>
-    </row>
-    <row r="231" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI230" s="4"/>
+      <c r="BJ230" s="4"/>
+      <c r="BK230" s="4"/>
+      <c r="BL230" s="4"/>
+    </row>
+    <row r="231" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
@@ -15536,8 +16541,12 @@
       <c r="BF231" s="4"/>
       <c r="BG231" s="4"/>
       <c r="BH231" s="4"/>
-    </row>
-    <row r="232" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI231" s="4"/>
+      <c r="BJ231" s="4"/>
+      <c r="BK231" s="4"/>
+      <c r="BL231" s="4"/>
+    </row>
+    <row r="232" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
@@ -15596,8 +16605,12 @@
       <c r="BF232" s="4"/>
       <c r="BG232" s="4"/>
       <c r="BH232" s="4"/>
-    </row>
-    <row r="233" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI232" s="4"/>
+      <c r="BJ232" s="4"/>
+      <c r="BK232" s="4"/>
+      <c r="BL232" s="4"/>
+    </row>
+    <row r="233" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
@@ -15656,8 +16669,12 @@
       <c r="BF233" s="4"/>
       <c r="BG233" s="4"/>
       <c r="BH233" s="4"/>
-    </row>
-    <row r="234" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI233" s="4"/>
+      <c r="BJ233" s="4"/>
+      <c r="BK233" s="4"/>
+      <c r="BL233" s="4"/>
+    </row>
+    <row r="234" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
@@ -15716,8 +16733,12 @@
       <c r="BF234" s="4"/>
       <c r="BG234" s="4"/>
       <c r="BH234" s="4"/>
-    </row>
-    <row r="235" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI234" s="4"/>
+      <c r="BJ234" s="4"/>
+      <c r="BK234" s="4"/>
+      <c r="BL234" s="4"/>
+    </row>
+    <row r="235" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
@@ -15776,8 +16797,12 @@
       <c r="BF235" s="4"/>
       <c r="BG235" s="4"/>
       <c r="BH235" s="4"/>
-    </row>
-    <row r="236" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI235" s="4"/>
+      <c r="BJ235" s="4"/>
+      <c r="BK235" s="4"/>
+      <c r="BL235" s="4"/>
+    </row>
+    <row r="236" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
@@ -15836,8 +16861,12 @@
       <c r="BF236" s="4"/>
       <c r="BG236" s="4"/>
       <c r="BH236" s="4"/>
-    </row>
-    <row r="237" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI236" s="4"/>
+      <c r="BJ236" s="4"/>
+      <c r="BK236" s="4"/>
+      <c r="BL236" s="4"/>
+    </row>
+    <row r="237" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
@@ -15896,8 +16925,12 @@
       <c r="BF237" s="4"/>
       <c r="BG237" s="4"/>
       <c r="BH237" s="4"/>
-    </row>
-    <row r="238" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI237" s="4"/>
+      <c r="BJ237" s="4"/>
+      <c r="BK237" s="4"/>
+      <c r="BL237" s="4"/>
+    </row>
+    <row r="238" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
@@ -15956,8 +16989,12 @@
       <c r="BF238" s="4"/>
       <c r="BG238" s="4"/>
       <c r="BH238" s="4"/>
-    </row>
-    <row r="239" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI238" s="4"/>
+      <c r="BJ238" s="4"/>
+      <c r="BK238" s="4"/>
+      <c r="BL238" s="4"/>
+    </row>
+    <row r="239" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
@@ -16016,8 +17053,12 @@
       <c r="BF239" s="4"/>
       <c r="BG239" s="4"/>
       <c r="BH239" s="4"/>
-    </row>
-    <row r="240" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI239" s="4"/>
+      <c r="BJ239" s="4"/>
+      <c r="BK239" s="4"/>
+      <c r="BL239" s="4"/>
+    </row>
+    <row r="240" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
@@ -16076,8 +17117,12 @@
       <c r="BF240" s="4"/>
       <c r="BG240" s="4"/>
       <c r="BH240" s="4"/>
-    </row>
-    <row r="241" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI240" s="4"/>
+      <c r="BJ240" s="4"/>
+      <c r="BK240" s="4"/>
+      <c r="BL240" s="4"/>
+    </row>
+    <row r="241" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
@@ -16136,8 +17181,12 @@
       <c r="BF241" s="4"/>
       <c r="BG241" s="4"/>
       <c r="BH241" s="4"/>
-    </row>
-    <row r="242" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI241" s="4"/>
+      <c r="BJ241" s="4"/>
+      <c r="BK241" s="4"/>
+      <c r="BL241" s="4"/>
+    </row>
+    <row r="242" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
@@ -16196,8 +17245,12 @@
       <c r="BF242" s="4"/>
       <c r="BG242" s="4"/>
       <c r="BH242" s="4"/>
-    </row>
-    <row r="243" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI242" s="4"/>
+      <c r="BJ242" s="4"/>
+      <c r="BK242" s="4"/>
+      <c r="BL242" s="4"/>
+    </row>
+    <row r="243" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
@@ -16256,8 +17309,12 @@
       <c r="BF243" s="4"/>
       <c r="BG243" s="4"/>
       <c r="BH243" s="4"/>
-    </row>
-    <row r="244" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI243" s="4"/>
+      <c r="BJ243" s="4"/>
+      <c r="BK243" s="4"/>
+      <c r="BL243" s="4"/>
+    </row>
+    <row r="244" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
@@ -16316,8 +17373,12 @@
       <c r="BF244" s="4"/>
       <c r="BG244" s="4"/>
       <c r="BH244" s="4"/>
-    </row>
-    <row r="245" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI244" s="4"/>
+      <c r="BJ244" s="4"/>
+      <c r="BK244" s="4"/>
+      <c r="BL244" s="4"/>
+    </row>
+    <row r="245" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
@@ -16376,8 +17437,12 @@
       <c r="BF245" s="4"/>
       <c r="BG245" s="4"/>
       <c r="BH245" s="4"/>
-    </row>
-    <row r="246" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI245" s="4"/>
+      <c r="BJ245" s="4"/>
+      <c r="BK245" s="4"/>
+      <c r="BL245" s="4"/>
+    </row>
+    <row r="246" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
@@ -16436,8 +17501,12 @@
       <c r="BF246" s="4"/>
       <c r="BG246" s="4"/>
       <c r="BH246" s="4"/>
-    </row>
-    <row r="247" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI246" s="4"/>
+      <c r="BJ246" s="4"/>
+      <c r="BK246" s="4"/>
+      <c r="BL246" s="4"/>
+    </row>
+    <row r="247" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
@@ -16496,8 +17565,12 @@
       <c r="BF247" s="4"/>
       <c r="BG247" s="4"/>
       <c r="BH247" s="4"/>
-    </row>
-    <row r="248" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI247" s="4"/>
+      <c r="BJ247" s="4"/>
+      <c r="BK247" s="4"/>
+      <c r="BL247" s="4"/>
+    </row>
+    <row r="248" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
@@ -16556,8 +17629,12 @@
       <c r="BF248" s="4"/>
       <c r="BG248" s="4"/>
       <c r="BH248" s="4"/>
-    </row>
-    <row r="249" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI248" s="4"/>
+      <c r="BJ248" s="4"/>
+      <c r="BK248" s="4"/>
+      <c r="BL248" s="4"/>
+    </row>
+    <row r="249" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
@@ -16616,8 +17693,12 @@
       <c r="BF249" s="4"/>
       <c r="BG249" s="4"/>
       <c r="BH249" s="4"/>
-    </row>
-    <row r="250" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI249" s="4"/>
+      <c r="BJ249" s="4"/>
+      <c r="BK249" s="4"/>
+      <c r="BL249" s="4"/>
+    </row>
+    <row r="250" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
@@ -16676,8 +17757,12 @@
       <c r="BF250" s="4"/>
       <c r="BG250" s="4"/>
       <c r="BH250" s="4"/>
-    </row>
-    <row r="251" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI250" s="4"/>
+      <c r="BJ250" s="4"/>
+      <c r="BK250" s="4"/>
+      <c r="BL250" s="4"/>
+    </row>
+    <row r="251" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
@@ -16736,8 +17821,12 @@
       <c r="BF251" s="4"/>
       <c r="BG251" s="4"/>
       <c r="BH251" s="4"/>
-    </row>
-    <row r="252" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI251" s="4"/>
+      <c r="BJ251" s="4"/>
+      <c r="BK251" s="4"/>
+      <c r="BL251" s="4"/>
+    </row>
+    <row r="252" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
@@ -16796,8 +17885,12 @@
       <c r="BF252" s="4"/>
       <c r="BG252" s="4"/>
       <c r="BH252" s="4"/>
-    </row>
-    <row r="253" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI252" s="4"/>
+      <c r="BJ252" s="4"/>
+      <c r="BK252" s="4"/>
+      <c r="BL252" s="4"/>
+    </row>
+    <row r="253" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
@@ -16856,8 +17949,12 @@
       <c r="BF253" s="4"/>
       <c r="BG253" s="4"/>
       <c r="BH253" s="4"/>
-    </row>
-    <row r="254" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI253" s="4"/>
+      <c r="BJ253" s="4"/>
+      <c r="BK253" s="4"/>
+      <c r="BL253" s="4"/>
+    </row>
+    <row r="254" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
@@ -16916,8 +18013,12 @@
       <c r="BF254" s="4"/>
       <c r="BG254" s="4"/>
       <c r="BH254" s="4"/>
-    </row>
-    <row r="255" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI254" s="4"/>
+      <c r="BJ254" s="4"/>
+      <c r="BK254" s="4"/>
+      <c r="BL254" s="4"/>
+    </row>
+    <row r="255" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
@@ -16976,8 +18077,12 @@
       <c r="BF255" s="4"/>
       <c r="BG255" s="4"/>
       <c r="BH255" s="4"/>
-    </row>
-    <row r="256" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI255" s="4"/>
+      <c r="BJ255" s="4"/>
+      <c r="BK255" s="4"/>
+      <c r="BL255" s="4"/>
+    </row>
+    <row r="256" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
@@ -17036,8 +18141,12 @@
       <c r="BF256" s="4"/>
       <c r="BG256" s="4"/>
       <c r="BH256" s="4"/>
-    </row>
-    <row r="257" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI256" s="4"/>
+      <c r="BJ256" s="4"/>
+      <c r="BK256" s="4"/>
+      <c r="BL256" s="4"/>
+    </row>
+    <row r="257" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
@@ -17096,8 +18205,12 @@
       <c r="BF257" s="4"/>
       <c r="BG257" s="4"/>
       <c r="BH257" s="4"/>
-    </row>
-    <row r="258" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI257" s="4"/>
+      <c r="BJ257" s="4"/>
+      <c r="BK257" s="4"/>
+      <c r="BL257" s="4"/>
+    </row>
+    <row r="258" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
@@ -17156,8 +18269,12 @@
       <c r="BF258" s="4"/>
       <c r="BG258" s="4"/>
       <c r="BH258" s="4"/>
-    </row>
-    <row r="259" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI258" s="4"/>
+      <c r="BJ258" s="4"/>
+      <c r="BK258" s="4"/>
+      <c r="BL258" s="4"/>
+    </row>
+    <row r="259" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
@@ -17216,8 +18333,12 @@
       <c r="BF259" s="4"/>
       <c r="BG259" s="4"/>
       <c r="BH259" s="4"/>
-    </row>
-    <row r="260" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI259" s="4"/>
+      <c r="BJ259" s="4"/>
+      <c r="BK259" s="4"/>
+      <c r="BL259" s="4"/>
+    </row>
+    <row r="260" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
@@ -17276,8 +18397,12 @@
       <c r="BF260" s="4"/>
       <c r="BG260" s="4"/>
       <c r="BH260" s="4"/>
-    </row>
-    <row r="261" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI260" s="4"/>
+      <c r="BJ260" s="4"/>
+      <c r="BK260" s="4"/>
+      <c r="BL260" s="4"/>
+    </row>
+    <row r="261" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
@@ -17336,8 +18461,12 @@
       <c r="BF261" s="4"/>
       <c r="BG261" s="4"/>
       <c r="BH261" s="4"/>
-    </row>
-    <row r="262" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI261" s="4"/>
+      <c r="BJ261" s="4"/>
+      <c r="BK261" s="4"/>
+      <c r="BL261" s="4"/>
+    </row>
+    <row r="262" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
@@ -17396,8 +18525,12 @@
       <c r="BF262" s="4"/>
       <c r="BG262" s="4"/>
       <c r="BH262" s="4"/>
-    </row>
-    <row r="263" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI262" s="4"/>
+      <c r="BJ262" s="4"/>
+      <c r="BK262" s="4"/>
+      <c r="BL262" s="4"/>
+    </row>
+    <row r="263" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
@@ -17456,8 +18589,12 @@
       <c r="BF263" s="4"/>
       <c r="BG263" s="4"/>
       <c r="BH263" s="4"/>
-    </row>
-    <row r="264" spans="3:60" x14ac:dyDescent="0.2">
+      <c r="BI263" s="4"/>
+      <c r="BJ263" s="4"/>
+      <c r="BK263" s="4"/>
+      <c r="BL263" s="4"/>
+    </row>
+    <row r="264" spans="3:64" x14ac:dyDescent="0.2">
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
@@ -17516,6 +18653,10 @@
       <c r="BF264" s="4"/>
       <c r="BG264" s="4"/>
       <c r="BH264" s="4"/>
+      <c r="BI264" s="4"/>
+      <c r="BJ264" s="4"/>
+      <c r="BK264" s="4"/>
+      <c r="BL264" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
